--- a/docs/An-field様_給与計算完全移管_進行管理_2026年9-10月.xlsx
+++ b/docs/An-field様_給与計算完全移管_進行管理_2026年9-10月.xlsx
@@ -23,7 +23,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="12">
+  <numFmts count="14">
     <numFmt numFmtId="164" formatCode="0.0&quot;h&quot;"/>
     <numFmt numFmtId="165" formatCode="0&quot;h&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot;名&quot;"/>
@@ -36,8 +36,10 @@
     <numFmt numFmtId="173" formatCode="0.0%"/>
     <numFmt numFmtId="174" formatCode="0&quot;社&quot;"/>
     <numFmt numFmtId="175" formatCode="0.0&quot;社/週&quot;"/>
+    <numFmt numFmtId="176" formatCode="0&quot;社/月&quot;"/>
+    <numFmt numFmtId="177" formatCode="0.0&quot;社/人&quot;"/>
   </numFmts>
-  <fonts count="44">
+  <fonts count="45">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -235,6 +237,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="008A4B00"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
@@ -299,7 +307,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
@@ -433,6 +441,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="008A4B00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E7E7E7"/>
       </patternFill>
     </fill>
@@ -462,7 +475,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="40">
+  <borders count="48">
     <border>
       <left/>
       <right/>
@@ -1016,11 +1029,123 @@
         <color rgb="009C0006"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="008A4B00"/>
+      </left>
+      <right style="thin">
+        <color rgb="00EDF2FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="008A4B00"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00EDF2FA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00EDF2FA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00EDF2FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="008A4B00"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00EDF2FA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00EDF2FA"/>
+      </left>
+      <right style="medium">
+        <color rgb="008A4B00"/>
+      </right>
+      <top style="medium">
+        <color rgb="008A4B00"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00EDF2FA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="008A4B00"/>
+      </left>
+      <right style="thin">
+        <color rgb="00EDF2FA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00EDF2FA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00EDF2FA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00EDF2FA"/>
+      </left>
+      <right style="medium">
+        <color rgb="008A4B00"/>
+      </right>
+      <top style="thin">
+        <color rgb="00EDF2FA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00EDF2FA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="008A4B00"/>
+      </left>
+      <right style="thin">
+        <color rgb="00EDF2FA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00EDF2FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="008A4B00"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00EDF2FA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00EDF2FA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00EDF2FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="008A4B00"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00EDF2FA"/>
+      </left>
+      <right style="medium">
+        <color rgb="008A4B00"/>
+      </right>
+      <top style="thin">
+        <color rgb="00EDF2FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="008A4B00"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="203">
+  <cellXfs count="214">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1338,13 +1463,19 @@
     <xf numFmtId="174" fontId="26" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="175" fontId="26" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="26" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="26" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="26" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="175" fontId="25" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="26" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1405,6 +1536,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="28" fillId="12" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1412,38 +1548,50 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="33" fillId="12" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="30" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="12" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="33" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="34" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="33" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="174" fontId="34" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="33" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="174" fontId="34" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="33" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="34" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="35" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="33" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="34" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="173" fontId="25" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="35" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="173" fontId="36" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1464,9 +1612,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="174" fontId="36" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="174" fontId="37" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1482,16 +1627,19 @@
     <xf numFmtId="174" fontId="41" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="174" fontId="42" fillId="33" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="173" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="43" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="44" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3302,7 +3450,7 @@
       </c>
       <c r="H7" s="23" t="n"/>
       <c r="I7" s="24">
-        <f>IF('キャパシティ・必要人数'!$D$26=0,"",ROUNDUP(G7/'キャパシティ・必要人数'!$D$26,0))</f>
+        <f>IF('キャパシティ・必要人数'!$D$29=0,"",ROUNDUP(G7/'キャパシティ・必要人数'!$D$29,0))</f>
         <v/>
       </c>
       <c r="J7" s="25" t="n"/>
@@ -3363,7 +3511,7 @@
       </c>
       <c r="H8" s="23" t="n"/>
       <c r="I8" s="24">
-        <f>IF('キャパシティ・必要人数'!$D$26=0,"",ROUNDUP(G8/'キャパシティ・必要人数'!$D$26,0))</f>
+        <f>IF('キャパシティ・必要人数'!$D$29=0,"",ROUNDUP(G8/'キャパシティ・必要人数'!$D$29,0))</f>
         <v/>
       </c>
       <c r="J8" s="25" t="n"/>
@@ -3426,7 +3574,7 @@
       </c>
       <c r="H9" s="23" t="n"/>
       <c r="I9" s="24">
-        <f>IF('キャパシティ・必要人数'!$D$26=0,"",ROUNDUP(G9/'キャパシティ・必要人数'!$D$26,0))</f>
+        <f>IF('キャパシティ・必要人数'!$D$29=0,"",ROUNDUP(G9/'キャパシティ・必要人数'!$D$29,0))</f>
         <v/>
       </c>
       <c r="J9" s="25" t="n"/>
@@ -3491,7 +3639,7 @@
       </c>
       <c r="H10" s="23" t="n"/>
       <c r="I10" s="24">
-        <f>IF('キャパシティ・必要人数'!$D$26=0,"",ROUNDUP(G10/'キャパシティ・必要人数'!$D$26,0))</f>
+        <f>IF('キャパシティ・必要人数'!$D$29=0,"",ROUNDUP(G10/'キャパシティ・必要人数'!$D$29,0))</f>
         <v/>
       </c>
       <c r="J10" s="25" t="n"/>
@@ -3549,7 +3697,7 @@
       </c>
       <c r="H11" s="23" t="n"/>
       <c r="I11" s="24">
-        <f>IF('キャパシティ・必要人数'!$D$26=0,"",ROUNDUP(G11/'キャパシティ・必要人数'!$D$26,0))</f>
+        <f>IF('キャパシティ・必要人数'!$D$29=0,"",ROUNDUP(G11/'キャパシティ・必要人数'!$D$29,0))</f>
         <v/>
       </c>
       <c r="J11" s="25" t="n"/>
@@ -3608,7 +3756,7 @@
       </c>
       <c r="H12" s="23" t="n"/>
       <c r="I12" s="24">
-        <f>IF('キャパシティ・必要人数'!$D$26=0,"",ROUNDUP(G12/'キャパシティ・必要人数'!$D$26,0))</f>
+        <f>IF('キャパシティ・必要人数'!$D$29=0,"",ROUNDUP(G12/'キャパシティ・必要人数'!$D$29,0))</f>
         <v/>
       </c>
       <c r="J12" s="25" t="n"/>
@@ -3668,7 +3816,7 @@
       </c>
       <c r="H13" s="23" t="n"/>
       <c r="I13" s="24">
-        <f>IF('キャパシティ・必要人数'!$D$26=0,"",ROUNDUP(G13/'キャパシティ・必要人数'!$D$26,0))</f>
+        <f>IF('キャパシティ・必要人数'!$D$29=0,"",ROUNDUP(G13/'キャパシティ・必要人数'!$D$29,0))</f>
         <v/>
       </c>
       <c r="J13" s="25" t="n"/>
@@ -3728,7 +3876,7 @@
       </c>
       <c r="H14" s="23" t="n"/>
       <c r="I14" s="24">
-        <f>IF('キャパシティ・必要人数'!$D$26=0,"",ROUNDUP(G14/'キャパシティ・必要人数'!$D$26,0))</f>
+        <f>IF('キャパシティ・必要人数'!$D$29=0,"",ROUNDUP(G14/'キャパシティ・必要人数'!$D$29,0))</f>
         <v/>
       </c>
       <c r="J14" s="25" t="n"/>
@@ -12771,7 +12919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -12843,7 +12991,7 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="121" t="inlineStr">
         <is>
-          <t>①　入力項目（薄い黄色セルを入力してください ／ すべて暫定値・要確認）</t>
+          <t>①　入力項目（薄い黄色セルを入力 ／ すべて暫定値・要確認・実績入力後に再計算）</t>
         </is>
       </c>
       <c r="B6" s="122" t="n"/>
@@ -12882,21 +13030,19 @@
     <row r="8" ht="22" customHeight="1">
       <c r="B8" s="123" t="inlineStr">
         <is>
-          <t>秘書チーム人数</t>
+          <t>対象企業総数</t>
         </is>
       </c>
       <c r="C8" s="19" t="n"/>
-      <c r="D8" s="124" t="n">
-        <v>3</v>
-      </c>
+      <c r="D8" s="124" t="n"/>
       <c r="E8" s="125" t="inlineStr">
         <is>
-          <t>名</t>
+          <t>社</t>
         </is>
       </c>
       <c r="F8" s="126" t="inlineStr">
         <is>
-          <t>全体管理・顧客対応・資料回収・質問対応・高難易度計算・教育・品質管理・納品管理・欠員時の再配置</t>
+          <t>【入力・空欄可】空欄の場合は案件進捗管理シートの企業名から自動集計します</t>
         </is>
       </c>
       <c r="G8" s="19" t="n"/>
@@ -12905,21 +13051,19 @@
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="123" t="inlineStr">
         <is>
-          <t>追加ワーカー人数</t>
+          <t>会社別総工数（月・合計）</t>
         </is>
       </c>
       <c r="C9" s="19" t="n"/>
-      <c r="D9" s="124" t="n">
-        <v>2</v>
-      </c>
+      <c r="D9" s="124" t="n"/>
       <c r="E9" s="125" t="inlineStr">
         <is>
-          <t>名</t>
+          <t>h/月</t>
         </is>
       </c>
       <c r="F9" s="126" t="inlineStr">
         <is>
-          <t>定型給与計算・チェックシートで自走可能な企業・手順が確立した業務</t>
+          <t>【入力・空欄可】空欄の場合は案件進捗管理シートの合計工数から自動集計します</t>
         </is>
       </c>
       <c r="G9" s="19" t="n"/>
@@ -12928,21 +13072,21 @@
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="123" t="inlineStr">
         <is>
-          <t>1人あたり週稼働可能時間</t>
+          <t>秘書チーム人数</t>
         </is>
       </c>
       <c r="C10" s="19" t="n"/>
       <c r="D10" s="124" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E10" s="125" t="inlineStr">
         <is>
-          <t>h/週</t>
+          <t>名</t>
         </is>
       </c>
       <c r="F10" s="126" t="inlineStr">
         <is>
-          <t>【暫定値・要確認】採用条件確定後に更新</t>
+          <t>全体管理・顧客対応・資料回収・質問対応・高難易度計算・教育・品質管理・納品管理・欠員時の再配置</t>
         </is>
       </c>
       <c r="G10" s="19" t="n"/>
@@ -12951,21 +13095,21 @@
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="123" t="inlineStr">
         <is>
-          <t>管理業務比率</t>
+          <t>追加ワーカー人数</t>
         </is>
       </c>
       <c r="C11" s="19" t="n"/>
-      <c r="D11" s="127" t="n">
-        <v>0.2</v>
+      <c r="D11" s="124" t="n">
+        <v>2</v>
       </c>
       <c r="E11" s="125" t="inlineStr">
         <is>
-          <t>％</t>
+          <t>名</t>
         </is>
       </c>
       <c r="F11" s="126" t="inlineStr">
         <is>
-          <t>【暫定値】打合せ・報告・調整など、直接作業以外に充てる割合</t>
+          <t>定型給与計算・チェックシートで自走可能な企業・手順が確立した業務</t>
         </is>
       </c>
       <c r="G11" s="19" t="n"/>
@@ -12974,12 +13118,12 @@
     <row r="12" ht="22" customHeight="1">
       <c r="B12" s="123" t="inlineStr">
         <is>
-          <t>教育工数（週・チーム全体）</t>
+          <t>1人あたり週稼働可能時間</t>
         </is>
       </c>
       <c r="C12" s="19" t="n"/>
       <c r="D12" s="124" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E12" s="125" t="inlineStr">
         <is>
@@ -12988,7 +13132,7 @@
       </c>
       <c r="F12" s="126" t="inlineStr">
         <is>
-          <t>【暫定値】追加ワーカー教育。処理可能工数から差し引く</t>
+          <t>【暫定値・要確認】採用条件確定後に更新</t>
         </is>
       </c>
       <c r="G12" s="19" t="n"/>
@@ -12997,21 +13141,21 @@
     <row r="13" ht="22" customHeight="1">
       <c r="B13" s="123" t="inlineStr">
         <is>
-          <t>品質確認工数（週・チーム全体）</t>
+          <t>管理業務比率</t>
         </is>
       </c>
       <c r="C13" s="19" t="n"/>
-      <c r="D13" s="124" t="n">
-        <v>8</v>
+      <c r="D13" s="127" t="n">
+        <v>0.2</v>
       </c>
       <c r="E13" s="125" t="inlineStr">
         <is>
-          <t>h/週</t>
+          <t>％</t>
         </is>
       </c>
       <c r="F13" s="126" t="inlineStr">
         <is>
-          <t>【暫定値】秘書チームによるチェック。処理可能工数から差し引く</t>
+          <t>【暫定値】打合せ・報告・調整など、直接作業以外に充てる割合</t>
         </is>
       </c>
       <c r="G13" s="19" t="n"/>
@@ -13020,21 +13164,21 @@
     <row r="14" ht="22" customHeight="1">
       <c r="B14" s="123" t="inlineStr">
         <is>
-          <t>難易度係数　A：標準</t>
+          <t>教育工数（週・チーム全体）</t>
         </is>
       </c>
       <c r="C14" s="19" t="n"/>
       <c r="D14" s="124" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E14" s="125" t="inlineStr">
         <is>
-          <t>倍</t>
+          <t>h/週</t>
         </is>
       </c>
       <c r="F14" s="126" t="inlineStr">
         <is>
-          <t>【暫定値】9/27までに基準確定。実績で更新</t>
+          <t>【暫定値】追加ワーカー教育。処理可能工数から差し引く</t>
         </is>
       </c>
       <c r="G14" s="19" t="n"/>
@@ -13043,21 +13187,21 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="123" t="inlineStr">
         <is>
-          <t>難易度係数　B：中程度</t>
+          <t>品質確認工数（週・チーム全体）</t>
         </is>
       </c>
       <c r="C15" s="19" t="n"/>
       <c r="D15" s="124" t="n">
-        <v>1.3</v>
+        <v>8</v>
       </c>
       <c r="E15" s="125" t="inlineStr">
         <is>
-          <t>倍</t>
+          <t>h/週</t>
         </is>
       </c>
       <c r="F15" s="126" t="inlineStr">
         <is>
-          <t>【暫定値】難易度未判定の企業にもこの係数を適用</t>
+          <t>【暫定値】秘書チームによるチェック。処理可能工数から差し引く</t>
         </is>
       </c>
       <c r="G15" s="19" t="n"/>
@@ -13066,21 +13210,21 @@
     <row r="16" ht="22" customHeight="1">
       <c r="B16" s="123" t="inlineStr">
         <is>
-          <t>難易度係数　C：複雑</t>
+          <t>移管1社あたり追加工数</t>
         </is>
       </c>
       <c r="C16" s="19" t="n"/>
       <c r="D16" s="124" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="E16" s="125" t="inlineStr">
         <is>
-          <t>倍</t>
+          <t>h/社</t>
         </is>
       </c>
       <c r="F16" s="126" t="inlineStr">
         <is>
-          <t>【暫定値】特殊ルール・例外処理が多い企業</t>
+          <t>【暫定値】引継ぎ・レクチャー・テスト計算・検証にかかる初期工数。月あたり移管可能件数の算定に使用</t>
         </is>
       </c>
       <c r="G16" s="19" t="n"/>
@@ -13089,156 +13233,154 @@
     <row r="17" ht="22" customHeight="1">
       <c r="B17" s="123" t="inlineStr">
         <is>
-          <t>月換算係数（週→月）</t>
+          <t>難易度係数　A：標準</t>
         </is>
       </c>
       <c r="C17" s="19" t="n"/>
-      <c r="D17" s="128" t="n">
-        <v>4.33</v>
+      <c r="D17" s="124" t="n">
+        <v>1</v>
       </c>
       <c r="E17" s="125" t="inlineStr">
         <is>
-          <t>週/月</t>
+          <t>倍</t>
         </is>
       </c>
       <c r="F17" s="126" t="inlineStr">
         <is>
-          <t>1ヶ月＝約4.33週</t>
+          <t>【暫定値】9/27までに基準確定。実績入力後に再計算</t>
         </is>
       </c>
       <c r="G17" s="19" t="n"/>
       <c r="H17" s="19" t="n"/>
     </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="123" t="inlineStr">
+        <is>
+          <t>難易度係数　B：中程度</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="124" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E18" s="125" t="inlineStr">
+        <is>
+          <t>倍</t>
+        </is>
+      </c>
+      <c r="F18" s="126" t="inlineStr">
+        <is>
+          <t>【暫定値】難易度未判定の企業にもこの係数を適用</t>
+        </is>
+      </c>
+      <c r="G18" s="19" t="n"/>
+      <c r="H18" s="19" t="n"/>
+    </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="121" t="inlineStr">
+      <c r="B19" s="123" t="inlineStr">
+        <is>
+          <t>難易度係数　C：複雑</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="124" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E19" s="125" t="inlineStr">
+        <is>
+          <t>倍</t>
+        </is>
+      </c>
+      <c r="F19" s="126" t="inlineStr">
+        <is>
+          <t>【暫定値】特殊ルール・例外処理が多い企業</t>
+        </is>
+      </c>
+      <c r="G19" s="19" t="n"/>
+      <c r="H19" s="19" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="123" t="inlineStr">
+        <is>
+          <t>月換算係数（週→月）</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="128" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E20" s="125" t="inlineStr">
+        <is>
+          <t>週/月</t>
+        </is>
+      </c>
+      <c r="F20" s="126" t="inlineStr">
+        <is>
+          <t>1ヶ月＝約4.33週</t>
+        </is>
+      </c>
+      <c r="G20" s="19" t="n"/>
+      <c r="H20" s="19" t="n"/>
+    </row>
+    <row r="21" ht="7" customHeight="1"/>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="121" t="inlineStr">
         <is>
           <t>②　自動計算（グレーのセル ／ 入力値と案件進捗管理シートから算出）</t>
         </is>
       </c>
-      <c r="B19" s="122" t="n"/>
-      <c r="C19" s="122" t="n"/>
-      <c r="D19" s="122" t="n"/>
-      <c r="E19" s="122" t="n"/>
-      <c r="F19" s="122" t="n"/>
-      <c r="G19" s="122" t="n"/>
-      <c r="H19" s="122" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B22" s="122" t="n"/>
+      <c r="C22" s="122" t="n"/>
+      <c r="D22" s="122" t="n"/>
+      <c r="E22" s="122" t="n"/>
+      <c r="F22" s="122" t="n"/>
+      <c r="G22" s="122" t="n"/>
+      <c r="H22" s="122" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C20" s="60" t="n"/>
-      <c r="D20" s="15" t="inlineStr">
+      <c r="C23" s="60" t="n"/>
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>値</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>単位</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="F23" s="15" t="inlineStr">
         <is>
           <t>計算式・考え方</t>
         </is>
       </c>
-      <c r="G20" s="60" t="n"/>
-      <c r="H20" s="60" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="123" t="inlineStr">
-        <is>
-          <t>対象企業総数</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="n"/>
-      <c r="D21" s="129">
-        <f>COUNTA('案件進捗管理'!$B$6:$B$115)</f>
-        <v/>
-      </c>
-      <c r="E21" s="125" t="inlineStr">
-        <is>
-          <t>社</t>
-        </is>
-      </c>
-      <c r="F21" s="126" t="inlineStr">
-        <is>
-          <t>案件進捗管理シートの企業名から自動集計</t>
-        </is>
-      </c>
-      <c r="G21" s="19" t="n"/>
-      <c r="H21" s="19" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="123" t="inlineStr">
-        <is>
-          <t>会社別総工数（月・単純合計）</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="n"/>
-      <c r="D22" s="130">
-        <f>SUM('案件進捗管理'!$Q$6:$Q$115)</f>
-        <v/>
-      </c>
-      <c r="E22" s="125" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="F22" s="126" t="inlineStr">
-        <is>
-          <t>各社の合計工数（給与計算＋資料回収＋顧客対応＋質問対応）の合計</t>
-        </is>
-      </c>
-      <c r="G22" s="19" t="n"/>
-      <c r="H22" s="19" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="B23" s="131" t="inlineStr">
-        <is>
-          <t>総必要工数（月・難易度調整後）</t>
-        </is>
-      </c>
-      <c r="C23" s="132" t="n"/>
-      <c r="D23" s="133">
-        <f>SUMIF('案件進捗管理'!$D$6:$D$115,"A：標準",'案件進捗管理'!$Q$6:$Q$115)*'キャパシティ・必要人数'!$D$14+SUMIF('案件進捗管理'!$D$6:$D$115,"B：中程度",'案件進捗管理'!$Q$6:$Q$115)*'キャパシティ・必要人数'!$D$15+SUMIF('案件進捗管理'!$D$6:$D$115,"C：複雑",'案件進捗管理'!$Q$6:$Q$115)*'キャパシティ・必要人数'!$D$16+('キャパシティ・必要人数'!$D$22-SUMIF('案件進捗管理'!$D$6:$D$115,"A：標準",'案件進捗管理'!$Q$6:$Q$115)-SUMIF('案件進捗管理'!$D$6:$D$115,"B：中程度",'案件進捗管理'!$Q$6:$Q$115)-SUMIF('案件進捗管理'!$D$6:$D$115,"C：複雑",'案件進捗管理'!$Q$6:$Q$115))*'キャパシティ・必要人数'!$D$15</f>
-        <v/>
-      </c>
-      <c r="E23" s="125" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="F23" s="126" t="inlineStr">
-        <is>
-          <t>会社別総工数 × 難易度係数。難易度未判定の企業はB係数で暫定計上</t>
-        </is>
-      </c>
-      <c r="G23" s="19" t="n"/>
-      <c r="H23" s="19" t="n"/>
+      <c r="G23" s="60" t="n"/>
+      <c r="H23" s="60" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="B24" s="123" t="inlineStr">
         <is>
-          <t>現在移管済み工数（月・単純合計）</t>
+          <t>対象企業総数（採用値）</t>
         </is>
       </c>
       <c r="C24" s="19" t="n"/>
-      <c r="D24" s="130">
-        <f>SUMIFS('案件進捗管理'!$Q$6:$Q$115,'案件進捗管理'!$V$6:$V$115,"&gt;0")</f>
+      <c r="D24" s="129">
+        <f>IF('キャパシティ・必要人数'!$D$8="",COUNTA('案件進捗管理'!$B$6:$B$115),'キャパシティ・必要人数'!$D$8)</f>
         <v/>
       </c>
       <c r="E24" s="125" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>社</t>
         </is>
       </c>
       <c r="F24" s="126" t="inlineStr">
         <is>
-          <t>実運用開始日が入力済みの企業の工数合計</t>
+          <t>入力欄が空欄なら案件進捗管理シートから自動集計</t>
         </is>
       </c>
       <c r="G24" s="19" t="n"/>
@@ -13247,12 +13389,12 @@
     <row r="25" ht="22" customHeight="1">
       <c r="B25" s="123" t="inlineStr">
         <is>
-          <t>残工数（月・単純合計）</t>
+          <t>会社別総工数（採用値・月）</t>
         </is>
       </c>
       <c r="C25" s="19" t="n"/>
       <c r="D25" s="130">
-        <f>'キャパシティ・必要人数'!$D$22-'キャパシティ・必要人数'!$D$24</f>
+        <f>IF('キャパシティ・必要人数'!$D$9="",SUM('案件進捗管理'!$Q$6:$Q$115),'キャパシティ・必要人数'!$D$9)</f>
         <v/>
       </c>
       <c r="E25" s="125" t="inlineStr">
@@ -13262,21 +13404,21 @@
       </c>
       <c r="F25" s="126" t="inlineStr">
         <is>
-          <t>会社別総工数 − 現在移管済み工数</t>
+          <t>入力欄が空欄なら各社の合計工数（給与計算＋資料回収＋顧客対応＋質問対応）を合計</t>
         </is>
       </c>
       <c r="G25" s="19" t="n"/>
       <c r="H25" s="19" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="B26" s="123" t="inlineStr">
-        <is>
-          <t>1人あたり週有効稼働時間</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="n"/>
-      <c r="D26" s="130">
-        <f>'キャパシティ・必要人数'!$D$10*(1-'キャパシティ・必要人数'!$D$11)</f>
+      <c r="B26" s="131" t="inlineStr">
+        <is>
+          <t>総必要工数（月・難易度調整後）</t>
+        </is>
+      </c>
+      <c r="C26" s="132" t="n"/>
+      <c r="D26" s="133">
+        <f>SUMIF('案件進捗管理'!$D$6:$D$115,"A：標準",'案件進捗管理'!$Q$6:$Q$115)*'キャパシティ・必要人数'!$D$17+SUMIF('案件進捗管理'!$D$6:$D$115,"B：中程度",'案件進捗管理'!$Q$6:$Q$115)*'キャパシティ・必要人数'!$D$18+SUMIF('案件進捗管理'!$D$6:$D$115,"C：複雑",'案件進捗管理'!$Q$6:$Q$115)*'キャパシティ・必要人数'!$D$19+MAX(0,'キャパシティ・必要人数'!$D$25-SUMIF('案件進捗管理'!$D$6:$D$115,"A：標準",'案件進捗管理'!$Q$6:$Q$115)-SUMIF('案件進捗管理'!$D$6:$D$115,"B：中程度",'案件進捗管理'!$Q$6:$Q$115)-SUMIF('案件進捗管理'!$D$6:$D$115,"C：複雑",'案件進捗管理'!$Q$6:$Q$115))*'キャパシティ・必要人数'!$D$18</f>
         <v/>
       </c>
       <c r="E26" s="125" t="inlineStr">
@@ -13286,7 +13428,7 @@
       </c>
       <c r="F26" s="126" t="inlineStr">
         <is>
-          <t>週稼働可能時間 ×（1 − 管理業務比率）</t>
+          <t>会社別総工数 × 難易度係数。難易度未判定の企業はB係数で暫定計上</t>
         </is>
       </c>
       <c r="G26" s="19" t="n"/>
@@ -13295,12 +13437,12 @@
     <row r="27" ht="22" customHeight="1">
       <c r="B27" s="123" t="inlineStr">
         <is>
-          <t>1人あたり月間有効稼働時間</t>
+          <t>現在移管済み工数（月）</t>
         </is>
       </c>
       <c r="C27" s="19" t="n"/>
       <c r="D27" s="130">
-        <f>'キャパシティ・必要人数'!$D$26*'キャパシティ・必要人数'!$D$17</f>
+        <f>SUMIFS('案件進捗管理'!$Q$6:$Q$115,'案件進捗管理'!$V$6:$V$115,"&gt;0")</f>
         <v/>
       </c>
       <c r="E27" s="125" t="inlineStr">
@@ -13310,7 +13452,7 @@
       </c>
       <c r="F27" s="126" t="inlineStr">
         <is>
-          <t>1人あたり週有効稼働時間 × 月換算係数</t>
+          <t>実運用開始日が入力済みの企業の工数合計</t>
         </is>
       </c>
       <c r="G27" s="19" t="n"/>
@@ -13319,12 +13461,12 @@
     <row r="28" ht="22" customHeight="1">
       <c r="B28" s="123" t="inlineStr">
         <is>
-          <t>週あたり処理可能工数</t>
+          <t>残工数（月）</t>
         </is>
       </c>
       <c r="C28" s="19" t="n"/>
       <c r="D28" s="130">
-        <f>('キャパシティ・必要人数'!$D$8+'キャパシティ・必要人数'!$D$9)*'キャパシティ・必要人数'!$D$26-'キャパシティ・必要人数'!$D$12-'キャパシティ・必要人数'!$D$13</f>
+        <f>'キャパシティ・必要人数'!$D$25-'キャパシティ・必要人数'!$D$27</f>
         <v/>
       </c>
       <c r="E28" s="125" t="inlineStr">
@@ -13334,7 +13476,7 @@
       </c>
       <c r="F28" s="126" t="inlineStr">
         <is>
-          <t>（秘書＋ワーカー）× 週有効稼働時間 − 教育工数 − 品質確認工数</t>
+          <t>会社別総工数 − 現在移管済み工数</t>
         </is>
       </c>
       <c r="G28" s="19" t="n"/>
@@ -13343,12 +13485,12 @@
     <row r="29" ht="22" customHeight="1">
       <c r="B29" s="123" t="inlineStr">
         <is>
-          <t>月あたり処理可能工数</t>
+          <t>1人あたり週有効稼働時間</t>
         </is>
       </c>
       <c r="C29" s="19" t="n"/>
       <c r="D29" s="130">
-        <f>'キャパシティ・必要人数'!$D$28*'キャパシティ・必要人数'!$D$17</f>
+        <f>'キャパシティ・必要人数'!$D$12*(1-'キャパシティ・必要人数'!$D$13)</f>
         <v/>
       </c>
       <c r="E29" s="125" t="inlineStr">
@@ -13358,7 +13500,7 @@
       </c>
       <c r="F29" s="126" t="inlineStr">
         <is>
-          <t>週あたり処理可能工数 × 月換算係数</t>
+          <t>週稼働可能時間 ×（1 − 管理業務比率）</t>
         </is>
       </c>
       <c r="G29" s="19" t="n"/>
@@ -13367,12 +13509,12 @@
     <row r="30" ht="22" customHeight="1">
       <c r="B30" s="123" t="inlineStr">
         <is>
-          <t>1社あたり平均工数（難易度調整後）</t>
+          <t>1人あたり処理可能工数（月）</t>
         </is>
       </c>
       <c r="C30" s="19" t="n"/>
       <c r="D30" s="130">
-        <f>IF(COUNTIF('案件進捗管理'!$Q$6:$Q$115,"&gt;0")=0,"",'キャパシティ・必要人数'!$D$23/COUNTIF('案件進捗管理'!$Q$6:$Q$115,"&gt;0"))</f>
+        <f>'キャパシティ・必要人数'!$D$29*'キャパシティ・必要人数'!$D$20</f>
         <v/>
       </c>
       <c r="E30" s="125" t="inlineStr">
@@ -13382,55 +13524,55 @@
       </c>
       <c r="F30" s="126" t="inlineStr">
         <is>
-          <t>総必要工数 ÷ 工数入力済み社数。※工数未入力の社が多いうちは参考値</t>
+          <t>1人あたり週有効稼働時間 × 月換算係数</t>
         </is>
       </c>
       <c r="G30" s="19" t="n"/>
       <c r="H30" s="19" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="B31" s="131" t="inlineStr">
-        <is>
-          <t>現在人数で処理可能な企業数</t>
-        </is>
-      </c>
-      <c r="C31" s="132" t="n"/>
-      <c r="D31" s="134">
-        <f>IF('キャパシティ・必要人数'!$D$30="","",ROUNDDOWN('キャパシティ・必要人数'!$D$29/'キャパシティ・必要人数'!$D$30,0))</f>
+      <c r="B31" s="123" t="inlineStr">
+        <is>
+          <t>週あたり処理可能工数（チーム）</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="130">
+        <f>('キャパシティ・必要人数'!$D$10+'キャパシティ・必要人数'!$D$11)*'キャパシティ・必要人数'!$D$29-'キャパシティ・必要人数'!$D$14-'キャパシティ・必要人数'!$D$15</f>
         <v/>
       </c>
       <c r="E31" s="125" t="inlineStr">
         <is>
-          <t>社</t>
+          <t>h</t>
         </is>
       </c>
       <c r="F31" s="126" t="inlineStr">
         <is>
-          <t>月あたり処理可能工数 ÷ 1社あたり平均工数</t>
+          <t>（秘書＋ワーカー）× 週有効稼働時間 − 教育工数 − 品質確認工数</t>
         </is>
       </c>
       <c r="G31" s="19" t="n"/>
       <c r="H31" s="19" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="131" t="inlineStr">
-        <is>
-          <t>必要追加人数</t>
-        </is>
-      </c>
-      <c r="C32" s="132" t="n"/>
-      <c r="D32" s="135">
-        <f>IF('キャパシティ・必要人数'!$D$23=0,"",MAX(0,ROUNDUP(('キャパシティ・必要人数'!$D$23-'キャパシティ・必要人数'!$D$29)/'キャパシティ・必要人数'!$D$27,0)))</f>
+      <c r="B32" s="123" t="inlineStr">
+        <is>
+          <t>月あたり処理可能工数（チーム）</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="130">
+        <f>'キャパシティ・必要人数'!$D$31*'キャパシティ・必要人数'!$D$20</f>
         <v/>
       </c>
       <c r="E32" s="125" t="inlineStr">
         <is>
-          <t>名</t>
+          <t>h</t>
         </is>
       </c>
       <c r="F32" s="126" t="inlineStr">
         <is>
-          <t>（総必要工数 − 月あたり処理可能工数）÷ 1人あたり月間有効稼働時間</t>
+          <t>週あたり処理可能工数 × 月換算係数</t>
         </is>
       </c>
       <c r="G32" s="19" t="n"/>
@@ -13439,36 +13581,36 @@
     <row r="33" ht="22" customHeight="1">
       <c r="B33" s="123" t="inlineStr">
         <is>
-          <t>現在の移管ペース（社/週）</t>
+          <t>1社あたり平均工数（難易度調整後）</t>
         </is>
       </c>
       <c r="C33" s="19" t="n"/>
-      <c r="D33" s="136">
-        <f>IF(TODAY()&lt;DATE(2026,9,9),"",COUNTIFS('案件進捗管理'!$V$6:$V$115,"&gt;0")/MIN(8,MAX(1,ROUNDDOWN((TODAY()-DATE(2026,9,9))/7,0)+1)))</f>
+      <c r="D33" s="130">
+        <f>IF(COUNTIF('案件進捗管理'!$Q$6:$Q$115,"&gt;0")=0,"",'キャパシティ・必要人数'!$D$26/COUNTIF('案件進捗管理'!$Q$6:$Q$115,"&gt;0"))</f>
         <v/>
       </c>
       <c r="E33" s="125" t="inlineStr">
         <is>
-          <t>社/週</t>
+          <t>h</t>
         </is>
       </c>
       <c r="F33" s="126" t="inlineStr">
         <is>
-          <t>実運用開始済み社数 ÷ 9/9からの経過週数（最大8週）</t>
+          <t>総必要工数 ÷ 工数入力済み社数。※工数未入力の社が多いうちは参考値（要確認）</t>
         </is>
       </c>
       <c r="G33" s="19" t="n"/>
       <c r="H33" s="19" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="123" t="inlineStr">
-        <is>
-          <t>完全移管までの残社数</t>
-        </is>
-      </c>
-      <c r="C34" s="19" t="n"/>
-      <c r="D34" s="129">
-        <f>'キャパシティ・必要人数'!$D$21-COUNTIFS('案件進捗管理'!$X$6:$X$115,"&gt;0")</f>
+      <c r="B34" s="131" t="inlineStr">
+        <is>
+          <t>現在人数で処理可能な企業数</t>
+        </is>
+      </c>
+      <c r="C34" s="132" t="n"/>
+      <c r="D34" s="134">
+        <f>IF('キャパシティ・必要人数'!$D$33="","",ROUNDDOWN('キャパシティ・必要人数'!$D$32/'キャパシティ・必要人数'!$D$33,0))</f>
         <v/>
       </c>
       <c r="E34" s="125" t="inlineStr">
@@ -13478,7 +13620,7 @@
       </c>
       <c r="F34" s="126" t="inlineStr">
         <is>
-          <t>対象企業総数 − 完全移管日が入力済みの社数</t>
+          <t>月あたり処理可能工数 ÷ 1社あたり平均工数（＝維持できる社数）</t>
         </is>
       </c>
       <c r="G34" s="19" t="n"/>
@@ -13491,8 +13633,8 @@
         </is>
       </c>
       <c r="C35" s="132" t="n"/>
-      <c r="D35" s="137">
-        <f>IF('キャパシティ・必要人数'!$D$30="","",'キャパシティ・必要人数'!$D$28/'キャパシティ・必要人数'!$D$30)</f>
+      <c r="D35" s="135">
+        <f>IF('キャパシティ・必要人数'!$D$33="","",'キャパシティ・必要人数'!$D$31/'キャパシティ・必要人数'!$D$33)</f>
         <v/>
       </c>
       <c r="E35" s="125" t="inlineStr">
@@ -13508,164 +13650,309 @@
       <c r="G35" s="19" t="n"/>
       <c r="H35" s="19" t="n"/>
     </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="B36" s="131" t="inlineStr">
+        <is>
+          <t>月あたり移管可能件数</t>
+        </is>
+      </c>
+      <c r="C36" s="132" t="n"/>
+      <c r="D36" s="136">
+        <f>IF('キャパシティ・必要人数'!$D$33="","",MAX(0,ROUNDDOWN(('キャパシティ・必要人数'!$D$32-'キャパシティ・必要人数'!$D$27)/('キャパシティ・必要人数'!$D$33+'キャパシティ・必要人数'!$D$16),0)))</f>
+        <v/>
+      </c>
+      <c r="E36" s="125" t="inlineStr">
+        <is>
+          <t>社/月</t>
+        </is>
+      </c>
+      <c r="F36" s="126" t="inlineStr">
+        <is>
+          <t>（月あたり処理可能工数 − 現在移管済み工数）÷（1社あたり平均工数 ＋ 移管1社あたり追加工数）</t>
+        </is>
+      </c>
+      <c r="G36" s="19" t="n"/>
+      <c r="H36" s="19" t="n"/>
+    </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="121" t="inlineStr">
+      <c r="B37" s="131" t="inlineStr">
+        <is>
+          <t>1人あたり処理可能社数（月）</t>
+        </is>
+      </c>
+      <c r="C37" s="132" t="n"/>
+      <c r="D37" s="137">
+        <f>IF('キャパシティ・必要人数'!$D$33="","",'キャパシティ・必要人数'!$D$30/'キャパシティ・必要人数'!$D$33)</f>
+        <v/>
+      </c>
+      <c r="E37" s="125" t="inlineStr">
+        <is>
+          <t>社/人</t>
+        </is>
+      </c>
+      <c r="F37" s="126" t="inlineStr">
+        <is>
+          <t>1人あたり処理可能工数（月）÷ 1社あたり平均工数</t>
+        </is>
+      </c>
+      <c r="G37" s="19" t="n"/>
+      <c r="H37" s="19" t="n"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="B38" s="131" t="inlineStr">
+        <is>
+          <t>必要追加人数</t>
+        </is>
+      </c>
+      <c r="C38" s="132" t="n"/>
+      <c r="D38" s="138">
+        <f>IF('キャパシティ・必要人数'!$D$26=0,"",MAX(0,ROUNDUP(('キャパシティ・必要人数'!$D$26-'キャパシティ・必要人数'!$D$32)/'キャパシティ・必要人数'!$D$30,0)))</f>
+        <v/>
+      </c>
+      <c r="E38" s="125" t="inlineStr">
+        <is>
+          <t>名</t>
+        </is>
+      </c>
+      <c r="F38" s="126" t="inlineStr">
+        <is>
+          <t>（総必要工数 − 月あたり処理可能工数）÷ 1人あたり処理可能工数（月）</t>
+        </is>
+      </c>
+      <c r="G38" s="19" t="n"/>
+      <c r="H38" s="19" t="n"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="B39" s="123" t="inlineStr">
+        <is>
+          <t>現在の移管ペース（社/週）</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="139">
+        <f>IF(TODAY()&lt;DATE(2026,9,9),"",COUNTIFS('案件進捗管理'!$V$6:$V$115,"&gt;0")/MIN(8,MAX(1,ROUNDDOWN((TODAY()-DATE(2026,9,9))/7,0)+1)))</f>
+        <v/>
+      </c>
+      <c r="E39" s="125" t="inlineStr">
+        <is>
+          <t>社/週</t>
+        </is>
+      </c>
+      <c r="F39" s="126" t="inlineStr">
+        <is>
+          <t>実運用開始済み社数 ÷ 9/9からの経過週数（最大8週）</t>
+        </is>
+      </c>
+      <c r="G39" s="19" t="n"/>
+      <c r="H39" s="19" t="n"/>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="B40" s="123" t="inlineStr">
+        <is>
+          <t>完全移管までの残社数</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="129">
+        <f>'キャパシティ・必要人数'!$D$24-COUNTIFS('案件進捗管理'!$X$6:$X$115,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="E40" s="125" t="inlineStr">
+        <is>
+          <t>社</t>
+        </is>
+      </c>
+      <c r="F40" s="126" t="inlineStr">
+        <is>
+          <t>対象企業総数 − 完全移管日が入力済みの社数</t>
+        </is>
+      </c>
+      <c r="G40" s="19" t="n"/>
+      <c r="H40" s="19" t="n"/>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="121" t="inlineStr">
         <is>
           <t>③　体制判定（自動）</t>
         </is>
       </c>
-      <c r="B37" s="122" t="n"/>
-      <c r="C37" s="122" t="n"/>
-      <c r="D37" s="122" t="n"/>
-      <c r="E37" s="122" t="n"/>
-      <c r="F37" s="122" t="n"/>
-      <c r="G37" s="122" t="n"/>
-      <c r="H37" s="122" t="n"/>
-    </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="B38" s="138">
-        <f>IF('キャパシティ・必要人数'!$D$23=0,"要確認：会社別工数が未入力のため判定できません（案件進捗管理シートに工数を入力してください）",IF('キャパシティ・必要人数'!$D$32=0,"OK：現在の人員（"&amp;('キャパシティ・必要人数'!$D$8+'キャパシティ・必要人数'!$D$9)&amp;"名）で対象企業を処理可能な試算です","要増員：追加 "&amp;'キャパシティ・必要人数'!$D$32&amp;"名が必要（暫定試算）　現在人数で処理可能なのは "&amp;'キャパシティ・必要人数'!$D$31&amp;" 社です"))</f>
-        <v/>
-      </c>
-      <c r="C38" s="41" t="n"/>
-      <c r="D38" s="41" t="n"/>
-      <c r="E38" s="41" t="n"/>
-      <c r="F38" s="41" t="n"/>
-      <c r="G38" s="41" t="n"/>
-      <c r="H38" s="41" t="n"/>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="B39" s="41" t="n"/>
-      <c r="C39" s="41" t="n"/>
-      <c r="D39" s="41" t="n"/>
-      <c r="E39" s="41" t="n"/>
-      <c r="F39" s="41" t="n"/>
-      <c r="G39" s="41" t="n"/>
-      <c r="H39" s="41" t="n"/>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="40" t="inlineStr">
-        <is>
-          <t>【このシートの使い方】件数ありきではなく工数ベースで計画します。案件進捗管理シートに各社の工数を入力するほど試算精度が上がります。工数が未入力の企業は「要確認」として合計に含まれません。</t>
-        </is>
-      </c>
-      <c r="B41" s="41" t="n"/>
-      <c r="C41" s="41" t="n"/>
-      <c r="D41" s="41" t="n"/>
-      <c r="E41" s="41" t="n"/>
-      <c r="F41" s="41" t="n"/>
-      <c r="G41" s="41" t="n"/>
-      <c r="H41" s="41" t="n"/>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="105" t="inlineStr">
-        <is>
-          <t>【再計算のタイミング】①9/20 先行企業の実工数計測後　②9/27 難易度A/B/C基準確定後　③10/18 会社別工数再計測後　④10/25 処理能力再計算・追加採用要否判定時。各時点で入力値を更新し、必要追加人数を見直してください。</t>
-        </is>
-      </c>
-      <c r="B42" s="43" t="n"/>
-      <c r="C42" s="43" t="n"/>
-      <c r="D42" s="43" t="n"/>
-      <c r="E42" s="43" t="n"/>
-      <c r="F42" s="43" t="n"/>
-      <c r="G42" s="43" t="n"/>
-      <c r="H42" s="43" t="n"/>
-    </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="139" t="inlineStr">
-        <is>
-          <t>【注意】難易度係数・週稼働可能時間・管理業務比率・教育工数・品質確認工数はすべて暫定値です。実績が出るまでは必要追加人数も暫定試算であり、確定値ではありません。</t>
-        </is>
-      </c>
-      <c r="B43" s="140" t="n"/>
-      <c r="C43" s="140" t="n"/>
-      <c r="D43" s="140" t="n"/>
-      <c r="E43" s="140" t="n"/>
-      <c r="F43" s="140" t="n"/>
-      <c r="G43" s="140" t="n"/>
-      <c r="H43" s="140" t="n"/>
+      <c r="B42" s="122" t="n"/>
+      <c r="C42" s="122" t="n"/>
+      <c r="D42" s="122" t="n"/>
+      <c r="E42" s="122" t="n"/>
+      <c r="F42" s="122" t="n"/>
+      <c r="G42" s="122" t="n"/>
+      <c r="H42" s="122" t="n"/>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="B43" s="140">
+        <f>IF('キャパシティ・必要人数'!$D$26=0,"要確認：会社別工数が未入力のため判定できません（案件進捗管理シートに工数を入力してください）",IF('キャパシティ・必要人数'!$D$38=0,"OK：現在の人員（"&amp;('キャパシティ・必要人数'!$D$10+'キャパシティ・必要人数'!$D$11)&amp;"名）で対象企業を処理可能な試算です　／月あたり移管可能件数 "&amp;'キャパシティ・必要人数'!$D$36&amp;" 社","要増員：追加 "&amp;'キャパシティ・必要人数'!$D$38&amp;"名が必要（暫定試算）　現在人数で処理可能なのは "&amp;'キャパシティ・必要人数'!$D$34&amp;" 社／月あたり移管可能件数 "&amp;'キャパシティ・必要人数'!$D$36&amp;" 社"))</f>
+        <v/>
+      </c>
+      <c r="C43" s="41" t="n"/>
+      <c r="D43" s="41" t="n"/>
+      <c r="E43" s="41" t="n"/>
+      <c r="F43" s="41" t="n"/>
+      <c r="G43" s="41" t="n"/>
+      <c r="H43" s="41" t="n"/>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="B44" s="41" t="n"/>
+      <c r="C44" s="41" t="n"/>
+      <c r="D44" s="41" t="n"/>
+      <c r="E44" s="41" t="n"/>
+      <c r="F44" s="41" t="n"/>
+      <c r="G44" s="41" t="n"/>
+      <c r="H44" s="41" t="n"/>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="40" t="inlineStr">
+        <is>
+          <t>【このシートの使い方】件数ありきではなく工数ベースで計画します。「対象企業総数」「会社別総工数」は空欄のままにすると案件進捗管理シートから自動集計され、数値を入力するとその値が優先されます（採用値は②に表示）。</t>
+        </is>
+      </c>
+      <c r="B46" s="41" t="n"/>
+      <c r="C46" s="41" t="n"/>
+      <c r="D46" s="41" t="n"/>
+      <c r="E46" s="41" t="n"/>
+      <c r="F46" s="41" t="n"/>
+      <c r="G46" s="41" t="n"/>
+      <c r="H46" s="41" t="n"/>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="39" t="inlineStr">
+        <is>
+          <t>【必要人数・処理可能社数・移管可能件数の関係】必要人数＝(総必要工数−月あたり処理可能工数)÷1人あたり処理可能工数　／　週あたり処理可能社数＝週あたり処理可能工数÷1社あたり平均工数　／　月あたり移管可能件数＝(月あたり処理可能工数−移管済み工数)÷(1社あたり平均工数＋移管1社あたり追加工数)</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="n"/>
+      <c r="C47" s="14" t="n"/>
+      <c r="D47" s="14" t="n"/>
+      <c r="E47" s="14" t="n"/>
+      <c r="F47" s="14" t="n"/>
+      <c r="G47" s="14" t="n"/>
+      <c r="H47" s="14" t="n"/>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="105" t="inlineStr">
+        <is>
+          <t>【再計算のタイミング】①9/20 先行企業の実工数計測後　②9/27 難易度A/B/C基準確定後　③10/18 会社別工数再計測後　④10/25 処理能力再計算・追加採用要否判定時。各時点で入力値を更新すると全ての試算が自動で再計算されます。</t>
+        </is>
+      </c>
+      <c r="B48" s="43" t="n"/>
+      <c r="C48" s="43" t="n"/>
+      <c r="D48" s="43" t="n"/>
+      <c r="E48" s="43" t="n"/>
+      <c r="F48" s="43" t="n"/>
+      <c r="G48" s="43" t="n"/>
+      <c r="H48" s="43" t="n"/>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="141" t="inlineStr">
+        <is>
+          <t>【暫定値・要確認】難易度係数・週稼働可能時間・管理業務比率・教育工数・品質確認工数・移管1社あたり追加工数はすべて暫定値です。実績が出るまで必要追加人数も暫定試算であり、確定値ではありません（実績入力後に再計算）。</t>
+        </is>
+      </c>
+      <c r="B49" s="142" t="n"/>
+      <c r="C49" s="142" t="n"/>
+      <c r="D49" s="142" t="n"/>
+      <c r="E49" s="142" t="n"/>
+      <c r="F49" s="142" t="n"/>
+      <c r="G49" s="142" t="n"/>
+      <c r="H49" s="142" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="69">
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B25:C25"/>
+  <mergeCells count="80">
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F18:H18"/>
     <mergeCell ref="F33:H33"/>
-    <mergeCell ref="F32:H32"/>
     <mergeCell ref="E7"/>
     <mergeCell ref="F8:H8"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A49:H49"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B27:C27"/>
     <mergeCell ref="A6:H6"/>
+    <mergeCell ref="D23"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B38:H39"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="D20"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A41:H41"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="F9:H9"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="F39:H39"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="F27:H27"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="E20"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="A42:H42"/>
-    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="A47:H47"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="F11:H11"/>
+    <mergeCell ref="A22:H22"/>
     <mergeCell ref="F25:H25"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D7"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="B43:H44"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="E23"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D7"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="B36:C36"/>
   </mergeCells>
-  <conditionalFormatting sqref="B38:H39">
+  <conditionalFormatting sqref="B43:H44">
     <cfRule type="expression" priority="1" dxfId="23">
-      <formula>ISNUMBER(SEARCH("要増員",$B$38))</formula>
+      <formula>ISNUMBER(SEARCH("要増員",$B$43))</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="24">
-      <formula>ISNUMBER(SEARCH("要確認",$B$38))</formula>
+      <formula>ISNUMBER(SEARCH("要確認",$B$43))</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="25">
-      <formula>ISNUMBER(SEARCH("OK：",$B$38))</formula>
+      <formula>ISNUMBER(SEARCH("OK：",$B$43))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13679,7 +13966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T112"/>
+  <dimension ref="A1:T114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -13835,385 +14122,399 @@
       <c r="T6" s="122" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="B7" s="141" t="inlineStr">
+      <c r="B7" s="143" t="inlineStr">
         <is>
           <t>総企業数</t>
         </is>
       </c>
-      <c r="C7" s="142" t="n"/>
-      <c r="D7" s="142" t="n"/>
-      <c r="E7" s="143" t="n"/>
-      <c r="G7" s="141" t="inlineStr">
+      <c r="C7" s="144" t="n"/>
+      <c r="D7" s="144" t="n"/>
+      <c r="E7" s="145" t="n"/>
+      <c r="G7" s="143" t="inlineStr">
         <is>
           <t>情報整理済み企業数</t>
         </is>
       </c>
-      <c r="H7" s="142" t="n"/>
-      <c r="I7" s="142" t="n"/>
-      <c r="J7" s="143" t="n"/>
-      <c r="L7" s="141" t="inlineStr">
+      <c r="H7" s="144" t="n"/>
+      <c r="I7" s="144" t="n"/>
+      <c r="J7" s="145" t="n"/>
+      <c r="L7" s="143" t="inlineStr">
         <is>
           <t>引継ぎ中企業数</t>
         </is>
       </c>
-      <c r="M7" s="142" t="n"/>
-      <c r="N7" s="142" t="n"/>
-      <c r="O7" s="143" t="n"/>
-      <c r="Q7" s="141" t="inlineStr">
+      <c r="M7" s="144" t="n"/>
+      <c r="N7" s="144" t="n"/>
+      <c r="O7" s="145" t="n"/>
+      <c r="Q7" s="143" t="inlineStr">
         <is>
           <t>初回計算済み企業数</t>
         </is>
       </c>
-      <c r="R7" s="142" t="n"/>
-      <c r="S7" s="142" t="n"/>
-      <c r="T7" s="143" t="n"/>
+      <c r="R7" s="144" t="n"/>
+      <c r="S7" s="144" t="n"/>
+      <c r="T7" s="145" t="n"/>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="B8" s="144">
+      <c r="B8" s="146">
         <f>COUNTA('案件進捗管理'!$B$6:$B$115)</f>
         <v/>
       </c>
-      <c r="C8" s="145" t="n"/>
-      <c r="D8" s="145" t="n"/>
-      <c r="E8" s="146" t="n"/>
-      <c r="G8" s="144">
+      <c r="C8" s="147" t="n"/>
+      <c r="D8" s="147" t="n"/>
+      <c r="E8" s="148" t="n"/>
+      <c r="G8" s="146">
         <f>SUMPRODUCT(('案件進捗管理'!$D$6:$D$115&lt;&gt;"")*('案件進捗管理'!$D$6:$D$115&lt;&gt;"未判定")*('案件進捗管理'!$Q$6:$Q$115&gt;0))</f>
         <v/>
       </c>
-      <c r="H8" s="145" t="n"/>
-      <c r="I8" s="145" t="n"/>
-      <c r="J8" s="146" t="n"/>
-      <c r="L8" s="144">
+      <c r="H8" s="147" t="n"/>
+      <c r="I8" s="147" t="n"/>
+      <c r="J8" s="148" t="n"/>
+      <c r="L8" s="146">
         <f>COUNTIF('案件進捗管理'!$E$6:$E$115,"2. 引継ぎ中")</f>
         <v/>
       </c>
-      <c r="M8" s="145" t="n"/>
-      <c r="N8" s="145" t="n"/>
-      <c r="O8" s="146" t="n"/>
-      <c r="Q8" s="144">
+      <c r="M8" s="147" t="n"/>
+      <c r="N8" s="147" t="n"/>
+      <c r="O8" s="148" t="n"/>
+      <c r="Q8" s="146">
         <f>SUMPRODUCT((('案件進捗管理'!$T$6:$T$115=TRUE)+('案件進捗管理'!$T$6:$T$115="TRUE")&gt;0)*1)</f>
         <v/>
       </c>
-      <c r="R8" s="145" t="n"/>
-      <c r="S8" s="145" t="n"/>
-      <c r="T8" s="146" t="n"/>
+      <c r="R8" s="147" t="n"/>
+      <c r="S8" s="147" t="n"/>
+      <c r="T8" s="148" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="147" t="inlineStr">
+      <c r="B9" s="149" t="inlineStr">
         <is>
           <t>対象 100〜110社</t>
         </is>
       </c>
-      <c r="C9" s="148" t="n"/>
-      <c r="D9" s="148" t="n"/>
-      <c r="E9" s="149" t="n"/>
-      <c r="G9" s="147" t="inlineStr">
+      <c r="C9" s="150" t="n"/>
+      <c r="D9" s="150" t="n"/>
+      <c r="E9" s="151" t="n"/>
+      <c r="G9" s="149" t="inlineStr">
         <is>
           <t>難易度が判定され、工数が入力済みの社数</t>
         </is>
       </c>
-      <c r="H9" s="148" t="n"/>
-      <c r="I9" s="148" t="n"/>
-      <c r="J9" s="149" t="n"/>
-      <c r="L9" s="147" t="inlineStr">
+      <c r="H9" s="150" t="n"/>
+      <c r="I9" s="150" t="n"/>
+      <c r="J9" s="151" t="n"/>
+      <c r="L9" s="149" t="inlineStr">
         <is>
           <t>ステータス＝2. 引継ぎ中</t>
         </is>
       </c>
-      <c r="M9" s="148" t="n"/>
-      <c r="N9" s="148" t="n"/>
-      <c r="O9" s="149" t="n"/>
-      <c r="Q9" s="147" t="inlineStr">
+      <c r="M9" s="150" t="n"/>
+      <c r="N9" s="150" t="n"/>
+      <c r="O9" s="151" t="n"/>
+      <c r="Q9" s="149" t="inlineStr">
         <is>
           <t>初回計算完了にチェックが入った社数</t>
         </is>
       </c>
-      <c r="R9" s="148" t="n"/>
-      <c r="S9" s="148" t="n"/>
-      <c r="T9" s="149" t="n"/>
+      <c r="R9" s="150" t="n"/>
+      <c r="S9" s="150" t="n"/>
+      <c r="T9" s="151" t="n"/>
     </row>
     <row r="10" ht="7" customHeight="1"/>
     <row r="11" ht="28" customHeight="1">
-      <c r="B11" s="141" t="inlineStr">
+      <c r="B11" s="143" t="inlineStr">
         <is>
           <t>検証中企業数</t>
         </is>
       </c>
-      <c r="C11" s="142" t="n"/>
-      <c r="D11" s="142" t="n"/>
-      <c r="E11" s="143" t="n"/>
-      <c r="G11" s="150" t="inlineStr">
+      <c r="C11" s="144" t="n"/>
+      <c r="D11" s="144" t="n"/>
+      <c r="E11" s="145" t="n"/>
+      <c r="G11" s="152" t="inlineStr">
         <is>
           <t>自走可能企業数</t>
         </is>
       </c>
-      <c r="H11" s="151" t="n"/>
-      <c r="I11" s="151" t="n"/>
-      <c r="J11" s="152" t="n"/>
-      <c r="L11" s="153" t="inlineStr">
+      <c r="H11" s="153" t="n"/>
+      <c r="I11" s="153" t="n"/>
+      <c r="J11" s="154" t="n"/>
+      <c r="L11" s="155" t="inlineStr">
         <is>
           <t>完全移管企業数</t>
         </is>
       </c>
-      <c r="M11" s="154" t="n"/>
-      <c r="N11" s="154" t="n"/>
-      <c r="O11" s="155" t="n"/>
-      <c r="Q11" s="141" t="inlineStr">
+      <c r="M11" s="156" t="n"/>
+      <c r="N11" s="156" t="n"/>
+      <c r="O11" s="157" t="n"/>
+      <c r="Q11" s="143" t="inlineStr">
         <is>
           <t>実運用累計企業数</t>
         </is>
       </c>
-      <c r="R11" s="142" t="n"/>
-      <c r="S11" s="142" t="n"/>
-      <c r="T11" s="143" t="n"/>
+      <c r="R11" s="144" t="n"/>
+      <c r="S11" s="144" t="n"/>
+      <c r="T11" s="145" t="n"/>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="B12" s="144">
+      <c r="B12" s="146">
         <f>COUNTIF('案件進捗管理'!$E$6:$E$115,"4. 検証中")</f>
         <v/>
       </c>
-      <c r="C12" s="145" t="n"/>
-      <c r="D12" s="145" t="n"/>
-      <c r="E12" s="146" t="n"/>
-      <c r="G12" s="156">
+      <c r="C12" s="147" t="n"/>
+      <c r="D12" s="147" t="n"/>
+      <c r="E12" s="148" t="n"/>
+      <c r="G12" s="158">
         <f>COUNTIFS('案件進捗管理'!$W$6:$W$115,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H12" s="145" t="n"/>
-      <c r="I12" s="145" t="n"/>
-      <c r="J12" s="157" t="n"/>
-      <c r="L12" s="158">
+      <c r="H12" s="147" t="n"/>
+      <c r="I12" s="147" t="n"/>
+      <c r="J12" s="159" t="n"/>
+      <c r="L12" s="160">
         <f>COUNTIFS('案件進捗管理'!$X$6:$X$115,"&gt;0")</f>
         <v/>
       </c>
-      <c r="M12" s="145" t="n"/>
-      <c r="N12" s="145" t="n"/>
-      <c r="O12" s="159" t="n"/>
-      <c r="Q12" s="144">
+      <c r="M12" s="147" t="n"/>
+      <c r="N12" s="147" t="n"/>
+      <c r="O12" s="161" t="n"/>
+      <c r="Q12" s="146">
         <f>COUNTIFS('案件進捗管理'!$V$6:$V$115,"&gt;0")</f>
         <v/>
       </c>
-      <c r="R12" s="145" t="n"/>
-      <c r="S12" s="145" t="n"/>
-      <c r="T12" s="146" t="n"/>
+      <c r="R12" s="147" t="n"/>
+      <c r="S12" s="147" t="n"/>
+      <c r="T12" s="148" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="147" t="inlineStr">
+      <c r="B13" s="149" t="inlineStr">
         <is>
           <t>ステータス＝4. 検証中</t>
         </is>
       </c>
-      <c r="C13" s="148" t="n"/>
-      <c r="D13" s="148" t="n"/>
-      <c r="E13" s="149" t="n"/>
-      <c r="G13" s="160" t="inlineStr">
-        <is>
-          <t>自走可能日が入力済みの社数</t>
-        </is>
-      </c>
-      <c r="H13" s="161" t="n"/>
-      <c r="I13" s="161" t="n"/>
-      <c r="J13" s="162" t="n"/>
-      <c r="L13" s="163" t="inlineStr">
-        <is>
-          <t>完全移管日が入力済み。An-field様の日常的な管理が不要な社数</t>
-        </is>
-      </c>
-      <c r="M13" s="164" t="n"/>
-      <c r="N13" s="164" t="n"/>
-      <c r="O13" s="165" t="n"/>
-      <c r="Q13" s="147" t="inlineStr">
+      <c r="C13" s="150" t="n"/>
+      <c r="D13" s="150" t="n"/>
+      <c r="E13" s="151" t="n"/>
+      <c r="G13" s="162" t="inlineStr">
+        <is>
+          <t>＝担当者単独で処理できた企業数（自走可能日が入力済み）</t>
+        </is>
+      </c>
+      <c r="H13" s="163" t="n"/>
+      <c r="I13" s="163" t="n"/>
+      <c r="J13" s="164" t="n"/>
+      <c r="L13" s="165" t="inlineStr">
+        <is>
+          <t>＝An-field様の確認が不要だった企業数（完全移管日が入力済み）</t>
+        </is>
+      </c>
+      <c r="M13" s="166" t="n"/>
+      <c r="N13" s="166" t="n"/>
+      <c r="O13" s="167" t="n"/>
+      <c r="Q13" s="149" t="inlineStr">
         <is>
           <t>実運用開始日が入力済みの社数</t>
         </is>
       </c>
-      <c r="R13" s="148" t="n"/>
-      <c r="S13" s="148" t="n"/>
-      <c r="T13" s="149" t="n"/>
+      <c r="R13" s="150" t="n"/>
+      <c r="S13" s="150" t="n"/>
+      <c r="T13" s="151" t="n"/>
     </row>
     <row r="14" ht="7" customHeight="1"/>
     <row r="15" ht="28" customHeight="1">
-      <c r="B15" s="141" t="inlineStr">
+      <c r="B15" s="143" t="inlineStr">
         <is>
           <t>移管済み工数</t>
         </is>
       </c>
-      <c r="C15" s="142" t="n"/>
-      <c r="D15" s="142" t="n"/>
-      <c r="E15" s="143" t="n"/>
-      <c r="G15" s="141" t="inlineStr">
+      <c r="C15" s="144" t="n"/>
+      <c r="D15" s="144" t="n"/>
+      <c r="E15" s="145" t="n"/>
+      <c r="G15" s="143" t="inlineStr">
         <is>
           <t>残工数</t>
         </is>
       </c>
-      <c r="H15" s="142" t="n"/>
-      <c r="I15" s="142" t="n"/>
-      <c r="J15" s="143" t="n"/>
-      <c r="L15" s="141" t="inlineStr">
+      <c r="H15" s="144" t="n"/>
+      <c r="I15" s="144" t="n"/>
+      <c r="J15" s="145" t="n"/>
+      <c r="L15" s="143" t="inlineStr">
         <is>
           <t>総実績工数</t>
         </is>
       </c>
-      <c r="M15" s="142" t="n"/>
-      <c r="N15" s="142" t="n"/>
-      <c r="O15" s="143" t="n"/>
-      <c r="Q15" s="141" t="inlineStr">
+      <c r="M15" s="144" t="n"/>
+      <c r="N15" s="144" t="n"/>
+      <c r="O15" s="145" t="n"/>
+      <c r="Q15" s="143" t="inlineStr">
         <is>
           <t>1社あたり平均工数</t>
         </is>
       </c>
-      <c r="R15" s="142" t="n"/>
-      <c r="S15" s="142" t="n"/>
-      <c r="T15" s="143" t="n"/>
+      <c r="R15" s="144" t="n"/>
+      <c r="S15" s="144" t="n"/>
+      <c r="T15" s="145" t="n"/>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="B16" s="166">
-        <f>'キャパシティ・必要人数'!$D$24</f>
-        <v/>
-      </c>
-      <c r="C16" s="145" t="n"/>
-      <c r="D16" s="145" t="n"/>
-      <c r="E16" s="146" t="n"/>
-      <c r="G16" s="166">
-        <f>'キャパシティ・必要人数'!$D$25</f>
-        <v/>
-      </c>
-      <c r="H16" s="145" t="n"/>
-      <c r="I16" s="145" t="n"/>
-      <c r="J16" s="146" t="n"/>
-      <c r="L16" s="166">
+      <c r="B16" s="168">
+        <f>'キャパシティ・必要人数'!$D$27</f>
+        <v/>
+      </c>
+      <c r="C16" s="147" t="n"/>
+      <c r="D16" s="147" t="n"/>
+      <c r="E16" s="148" t="n"/>
+      <c r="G16" s="168">
+        <f>'キャパシティ・必要人数'!$D$28</f>
+        <v/>
+      </c>
+      <c r="H16" s="147" t="n"/>
+      <c r="I16" s="147" t="n"/>
+      <c r="J16" s="148" t="n"/>
+      <c r="L16" s="168">
         <f>IF(COUNT('週間スケジュール'!$H$7:$H$14)=0,"",SUM('週間スケジュール'!$H$7:$H$14))</f>
         <v/>
       </c>
-      <c r="M16" s="145" t="n"/>
-      <c r="N16" s="145" t="n"/>
-      <c r="O16" s="146" t="n"/>
-      <c r="Q16" s="166">
+      <c r="M16" s="147" t="n"/>
+      <c r="N16" s="147" t="n"/>
+      <c r="O16" s="148" t="n"/>
+      <c r="Q16" s="168">
         <f>IF(COUNTIF('案件進捗管理'!$Q$6:$Q$115,"&gt;0")=0,"",SUM('案件進捗管理'!$Q$6:$Q$115)/COUNTIF('案件進捗管理'!$Q$6:$Q$115,"&gt;0"))</f>
         <v/>
       </c>
-      <c r="R16" s="145" t="n"/>
-      <c r="S16" s="145" t="n"/>
-      <c r="T16" s="146" t="n"/>
+      <c r="R16" s="147" t="n"/>
+      <c r="S16" s="147" t="n"/>
+      <c r="T16" s="148" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="147" t="inlineStr">
-        <is>
-          <t>実運用開始済み企業の月間工数合計</t>
-        </is>
-      </c>
-      <c r="C17" s="148" t="n"/>
-      <c r="D17" s="148" t="n"/>
-      <c r="E17" s="149" t="n"/>
-      <c r="G17" s="147" t="inlineStr">
+      <c r="B17" s="149" t="inlineStr">
+        <is>
+          <t>＝処理できた総工数（実運用開始済み企業の月間工数合計）</t>
+        </is>
+      </c>
+      <c r="C17" s="150" t="n"/>
+      <c r="D17" s="150" t="n"/>
+      <c r="E17" s="151" t="n"/>
+      <c r="G17" s="149" t="inlineStr">
         <is>
           <t>会社別総工数 − 移管済み工数（月）</t>
         </is>
       </c>
-      <c r="H17" s="148" t="n"/>
-      <c r="I17" s="148" t="n"/>
-      <c r="J17" s="149" t="n"/>
-      <c r="L17" s="147" t="inlineStr">
+      <c r="H17" s="150" t="n"/>
+      <c r="I17" s="150" t="n"/>
+      <c r="J17" s="151" t="n"/>
+      <c r="L17" s="149" t="inlineStr">
         <is>
           <t>週間スケジュールの実績工数の累計</t>
         </is>
       </c>
-      <c r="M17" s="148" t="n"/>
-      <c r="N17" s="148" t="n"/>
-      <c r="O17" s="149" t="n"/>
-      <c r="Q17" s="147" t="inlineStr">
+      <c r="M17" s="150" t="n"/>
+      <c r="N17" s="150" t="n"/>
+      <c r="O17" s="151" t="n"/>
+      <c r="Q17" s="149" t="inlineStr">
         <is>
           <t>工数入力済み社の単純平均（月）。難易度調整後はキャパシティシート参照</t>
         </is>
       </c>
-      <c r="R17" s="148" t="n"/>
-      <c r="S17" s="148" t="n"/>
-      <c r="T17" s="149" t="n"/>
+      <c r="R17" s="150" t="n"/>
+      <c r="S17" s="150" t="n"/>
+      <c r="T17" s="151" t="n"/>
     </row>
     <row r="18" ht="7" customHeight="1"/>
     <row r="19" ht="28" customHeight="1">
-      <c r="B19" s="141" t="inlineStr">
+      <c r="B19" s="143" t="inlineStr">
         <is>
           <t>現在人数</t>
         </is>
       </c>
-      <c r="C19" s="142" t="n"/>
-      <c r="D19" s="142" t="n"/>
-      <c r="E19" s="143" t="n"/>
-      <c r="G19" s="167" t="inlineStr">
+      <c r="C19" s="144" t="n"/>
+      <c r="D19" s="144" t="n"/>
+      <c r="E19" s="145" t="n"/>
+      <c r="G19" s="169" t="inlineStr">
         <is>
           <t>追加必要人数</t>
         </is>
       </c>
-      <c r="H19" s="168" t="n"/>
-      <c r="I19" s="168" t="n"/>
-      <c r="J19" s="169" t="n"/>
-      <c r="L19" s="40" t="inlineStr">
-        <is>
-          <t>【10月末時点で確認する判断材料】　① 実運用済み企業数　② 自走可能企業数　③ 完全移管企業数　④ 残企業数　⑤ 残工数　⑥ 必要追加人数　⑦ 1人あたり処理可能工数・処理可能社数　⑧ 今後の移管ペース（社/週）
-→ ⑦⑧は「キャパシティ・必要人数」シートで自動算出されます。</t>
-        </is>
-      </c>
-      <c r="M19" s="41" t="n"/>
-      <c r="N19" s="41" t="n"/>
-      <c r="O19" s="41" t="n"/>
-      <c r="P19" s="41" t="n"/>
-      <c r="Q19" s="41" t="n"/>
-      <c r="R19" s="41" t="n"/>
-      <c r="S19" s="41" t="n"/>
-      <c r="T19" s="41" t="n"/>
+      <c r="H19" s="170" t="n"/>
+      <c r="I19" s="170" t="n"/>
+      <c r="J19" s="171" t="n"/>
+      <c r="L19" s="172" t="inlineStr">
+        <is>
+          <t>月あたり移管可能件数</t>
+        </is>
+      </c>
+      <c r="M19" s="173" t="n"/>
+      <c r="N19" s="173" t="n"/>
+      <c r="O19" s="174" t="n"/>
+      <c r="Q19" s="152" t="inlineStr">
+        <is>
+          <t>1人あたり処理可能社数</t>
+        </is>
+      </c>
+      <c r="R19" s="153" t="n"/>
+      <c r="S19" s="153" t="n"/>
+      <c r="T19" s="154" t="n"/>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="B20" s="170">
-        <f>'キャパシティ・必要人数'!$D$8+'キャパシティ・必要人数'!$D$9</f>
-        <v/>
-      </c>
-      <c r="C20" s="145" t="n"/>
-      <c r="D20" s="145" t="n"/>
-      <c r="E20" s="146" t="n"/>
-      <c r="G20" s="171">
-        <f>'キャパシティ・必要人数'!$D$32</f>
-        <v/>
-      </c>
-      <c r="H20" s="145" t="n"/>
-      <c r="I20" s="145" t="n"/>
-      <c r="J20" s="172" t="n"/>
-      <c r="L20" s="41" t="n"/>
-      <c r="M20" s="41" t="n"/>
-      <c r="N20" s="41" t="n"/>
-      <c r="O20" s="41" t="n"/>
-      <c r="P20" s="41" t="n"/>
-      <c r="Q20" s="41" t="n"/>
-      <c r="R20" s="41" t="n"/>
-      <c r="S20" s="41" t="n"/>
-      <c r="T20" s="41" t="n"/>
+      <c r="B20" s="175">
+        <f>'キャパシティ・必要人数'!$D$10+'キャパシティ・必要人数'!$D$11</f>
+        <v/>
+      </c>
+      <c r="C20" s="147" t="n"/>
+      <c r="D20" s="147" t="n"/>
+      <c r="E20" s="148" t="n"/>
+      <c r="G20" s="176">
+        <f>'キャパシティ・必要人数'!$D$38</f>
+        <v/>
+      </c>
+      <c r="H20" s="147" t="n"/>
+      <c r="I20" s="147" t="n"/>
+      <c r="J20" s="177" t="n"/>
+      <c r="L20" s="178">
+        <f>'キャパシティ・必要人数'!$D$36</f>
+        <v/>
+      </c>
+      <c r="M20" s="147" t="n"/>
+      <c r="N20" s="147" t="n"/>
+      <c r="O20" s="179" t="n"/>
+      <c r="Q20" s="180">
+        <f>'キャパシティ・必要人数'!$D$37</f>
+        <v/>
+      </c>
+      <c r="R20" s="147" t="n"/>
+      <c r="S20" s="147" t="n"/>
+      <c r="T20" s="159" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="147" t="inlineStr">
+      <c r="B21" s="149" t="inlineStr">
         <is>
           <t>秘書チーム＋追加ワーカー</t>
         </is>
       </c>
-      <c r="C21" s="148" t="n"/>
-      <c r="D21" s="148" t="n"/>
-      <c r="E21" s="149" t="n"/>
-      <c r="G21" s="173" t="inlineStr">
-        <is>
-          <t>（総必要工数 − 月あたり処理可能工数）÷ 1人あたり月間有効稼働時間</t>
-        </is>
-      </c>
-      <c r="H21" s="174" t="n"/>
-      <c r="I21" s="174" t="n"/>
-      <c r="J21" s="175" t="n"/>
-      <c r="L21" s="41" t="n"/>
-      <c r="M21" s="41" t="n"/>
-      <c r="N21" s="41" t="n"/>
-      <c r="O21" s="41" t="n"/>
-      <c r="P21" s="41" t="n"/>
-      <c r="Q21" s="41" t="n"/>
-      <c r="R21" s="41" t="n"/>
-      <c r="S21" s="41" t="n"/>
-      <c r="T21" s="41" t="n"/>
+      <c r="C21" s="150" t="n"/>
+      <c r="D21" s="150" t="n"/>
+      <c r="E21" s="151" t="n"/>
+      <c r="G21" s="181" t="inlineStr">
+        <is>
+          <t>（総必要工数 − 月あたり処理可能工数）÷ 1人あたり処理可能工数（月）</t>
+        </is>
+      </c>
+      <c r="H21" s="182" t="n"/>
+      <c r="I21" s="182" t="n"/>
+      <c r="J21" s="183" t="n"/>
+      <c r="L21" s="184" t="inlineStr">
+        <is>
+          <t>（月処理可能工数 − 移管済み工数）÷（1社平均工数 ＋ 移管1社あたり追加工数）</t>
+        </is>
+      </c>
+      <c r="M21" s="185" t="n"/>
+      <c r="N21" s="185" t="n"/>
+      <c r="O21" s="186" t="n"/>
+      <c r="Q21" s="162" t="inlineStr">
+        <is>
+          <t>1人あたり処理可能工数（月）÷ 1社あたり平均工数</t>
+        </is>
+      </c>
+      <c r="R21" s="163" t="n"/>
+      <c r="S21" s="163" t="n"/>
+      <c r="T21" s="164" t="n"/>
     </row>
     <row r="22" ht="7" customHeight="1"/>
     <row r="24" ht="22" customHeight="1">
@@ -14307,383 +14608,383 @@
       <c r="T25" s="60" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="B26" s="176" t="inlineStr">
+      <c r="B26" s="187" t="inlineStr">
         <is>
           <t>第1週</t>
         </is>
       </c>
-      <c r="C26" s="177" t="n"/>
-      <c r="D26" s="178" t="n">
+      <c r="C26" s="188" t="n"/>
+      <c r="D26" s="189" t="n">
         <v>46278</v>
       </c>
-      <c r="E26" s="177" t="n"/>
-      <c r="F26" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="177" t="n"/>
-      <c r="H26" s="180">
+      <c r="E26" s="188" t="n"/>
+      <c r="F26" s="190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="188" t="n"/>
+      <c r="H26" s="191">
         <f>'週間スケジュール'!$F$7</f>
         <v/>
       </c>
       <c r="I26" s="45" t="n"/>
-      <c r="J26" s="181">
+      <c r="J26" s="192">
         <f>'週間スケジュール'!$G$7</f>
         <v/>
       </c>
-      <c r="K26" s="177" t="n"/>
-      <c r="L26" s="182">
+      <c r="K26" s="188" t="n"/>
+      <c r="L26" s="193">
         <f>IF('週間スケジュール'!$H$7="","",'週間スケジュール'!$H$7)</f>
         <v/>
       </c>
-      <c r="M26" s="183" t="n"/>
-      <c r="N26" s="184">
+      <c r="M26" s="194" t="n"/>
+      <c r="N26" s="195">
         <f>SUMPRODUCT(('案件進捗管理'!$V$6:$V$115&lt;&gt;"")*('案件進捗管理'!$V$6:$V$115&lt;=$D26)*'案件進捗管理'!$Q$6:$Q$115)</f>
         <v/>
       </c>
       <c r="O26" s="45" t="n"/>
-      <c r="P26" s="185">
-        <f>IF('キャパシティ・必要人数'!$D$21=0,"",H26/'キャパシティ・必要人数'!$D$21)</f>
+      <c r="P26" s="196">
+        <f>IF('キャパシティ・必要人数'!$D$24=0,"",H26/'キャパシティ・必要人数'!$D$24)</f>
         <v/>
       </c>
       <c r="Q26" s="45" t="n"/>
-      <c r="R26" s="186">
-        <f>IF('キャパシティ・必要人数'!$D$22=0,"",N26/'キャパシティ・必要人数'!$D$22)</f>
+      <c r="R26" s="197">
+        <f>IF('キャパシティ・必要人数'!$D$25=0,"",N26/'キャパシティ・必要人数'!$D$25)</f>
         <v/>
       </c>
       <c r="S26" s="45" t="n"/>
       <c r="T26" s="45" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="176" t="inlineStr">
+      <c r="B27" s="187" t="inlineStr">
         <is>
           <t>第2週</t>
         </is>
       </c>
-      <c r="C27" s="177" t="n"/>
-      <c r="D27" s="178" t="n">
+      <c r="C27" s="188" t="n"/>
+      <c r="D27" s="189" t="n">
         <v>46285</v>
       </c>
-      <c r="E27" s="177" t="n"/>
-      <c r="F27" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="177" t="n"/>
-      <c r="H27" s="180">
+      <c r="E27" s="188" t="n"/>
+      <c r="F27" s="190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="188" t="n"/>
+      <c r="H27" s="191">
         <f>'週間スケジュール'!$F$8</f>
         <v/>
       </c>
       <c r="I27" s="45" t="n"/>
-      <c r="J27" s="181">
+      <c r="J27" s="192">
         <f>'週間スケジュール'!$G$8</f>
         <v/>
       </c>
-      <c r="K27" s="177" t="n"/>
-      <c r="L27" s="182">
+      <c r="K27" s="188" t="n"/>
+      <c r="L27" s="193">
         <f>IF('週間スケジュール'!$H$8="","",'週間スケジュール'!$H$8)</f>
         <v/>
       </c>
-      <c r="M27" s="183" t="n"/>
-      <c r="N27" s="184">
+      <c r="M27" s="194" t="n"/>
+      <c r="N27" s="195">
         <f>SUMPRODUCT(('案件進捗管理'!$V$6:$V$115&lt;&gt;"")*('案件進捗管理'!$V$6:$V$115&lt;=$D27)*'案件進捗管理'!$Q$6:$Q$115)</f>
         <v/>
       </c>
       <c r="O27" s="45" t="n"/>
-      <c r="P27" s="185">
-        <f>IF('キャパシティ・必要人数'!$D$21=0,"",H27/'キャパシティ・必要人数'!$D$21)</f>
+      <c r="P27" s="196">
+        <f>IF('キャパシティ・必要人数'!$D$24=0,"",H27/'キャパシティ・必要人数'!$D$24)</f>
         <v/>
       </c>
       <c r="Q27" s="45" t="n"/>
-      <c r="R27" s="186">
-        <f>IF('キャパシティ・必要人数'!$D$22=0,"",N27/'キャパシティ・必要人数'!$D$22)</f>
+      <c r="R27" s="197">
+        <f>IF('キャパシティ・必要人数'!$D$25=0,"",N27/'キャパシティ・必要人数'!$D$25)</f>
         <v/>
       </c>
       <c r="S27" s="45" t="n"/>
       <c r="T27" s="45" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="176" t="inlineStr">
+      <c r="B28" s="187" t="inlineStr">
         <is>
           <t>第3週</t>
         </is>
       </c>
-      <c r="C28" s="177" t="n"/>
-      <c r="D28" s="178" t="n">
+      <c r="C28" s="188" t="n"/>
+      <c r="D28" s="189" t="n">
         <v>46292</v>
       </c>
-      <c r="E28" s="177" t="n"/>
-      <c r="F28" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="177" t="n"/>
-      <c r="H28" s="180">
+      <c r="E28" s="188" t="n"/>
+      <c r="F28" s="190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="188" t="n"/>
+      <c r="H28" s="191">
         <f>'週間スケジュール'!$F$9</f>
         <v/>
       </c>
       <c r="I28" s="45" t="n"/>
-      <c r="J28" s="181">
+      <c r="J28" s="192">
         <f>'週間スケジュール'!$G$9</f>
         <v/>
       </c>
-      <c r="K28" s="177" t="n"/>
-      <c r="L28" s="182">
+      <c r="K28" s="188" t="n"/>
+      <c r="L28" s="193">
         <f>IF('週間スケジュール'!$H$9="","",'週間スケジュール'!$H$9)</f>
         <v/>
       </c>
-      <c r="M28" s="183" t="n"/>
-      <c r="N28" s="184">
+      <c r="M28" s="194" t="n"/>
+      <c r="N28" s="195">
         <f>SUMPRODUCT(('案件進捗管理'!$V$6:$V$115&lt;&gt;"")*('案件進捗管理'!$V$6:$V$115&lt;=$D28)*'案件進捗管理'!$Q$6:$Q$115)</f>
         <v/>
       </c>
       <c r="O28" s="45" t="n"/>
-      <c r="P28" s="185">
-        <f>IF('キャパシティ・必要人数'!$D$21=0,"",H28/'キャパシティ・必要人数'!$D$21)</f>
+      <c r="P28" s="196">
+        <f>IF('キャパシティ・必要人数'!$D$24=0,"",H28/'キャパシティ・必要人数'!$D$24)</f>
         <v/>
       </c>
       <c r="Q28" s="45" t="n"/>
-      <c r="R28" s="186">
-        <f>IF('キャパシティ・必要人数'!$D$22=0,"",N28/'キャパシティ・必要人数'!$D$22)</f>
+      <c r="R28" s="197">
+        <f>IF('キャパシティ・必要人数'!$D$25=0,"",N28/'キャパシティ・必要人数'!$D$25)</f>
         <v/>
       </c>
       <c r="S28" s="45" t="n"/>
       <c r="T28" s="45" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="176" t="inlineStr">
+      <c r="B29" s="187" t="inlineStr">
         <is>
           <t>第4週</t>
         </is>
       </c>
-      <c r="C29" s="177" t="n"/>
-      <c r="D29" s="178" t="n">
+      <c r="C29" s="188" t="n"/>
+      <c r="D29" s="189" t="n">
         <v>46299</v>
       </c>
-      <c r="E29" s="177" t="n"/>
-      <c r="F29" s="179" t="n">
+      <c r="E29" s="188" t="n"/>
+      <c r="F29" s="190" t="n">
         <v>7</v>
       </c>
-      <c r="G29" s="177" t="n"/>
-      <c r="H29" s="180">
+      <c r="G29" s="188" t="n"/>
+      <c r="H29" s="191">
         <f>'週間スケジュール'!$F$10</f>
         <v/>
       </c>
       <c r="I29" s="45" t="n"/>
-      <c r="J29" s="181">
+      <c r="J29" s="192">
         <f>'週間スケジュール'!$G$10</f>
         <v/>
       </c>
-      <c r="K29" s="177" t="n"/>
-      <c r="L29" s="182">
+      <c r="K29" s="188" t="n"/>
+      <c r="L29" s="193">
         <f>IF('週間スケジュール'!$H$10="","",'週間スケジュール'!$H$10)</f>
         <v/>
       </c>
-      <c r="M29" s="183" t="n"/>
-      <c r="N29" s="184">
+      <c r="M29" s="194" t="n"/>
+      <c r="N29" s="195">
         <f>SUMPRODUCT(('案件進捗管理'!$V$6:$V$115&lt;&gt;"")*('案件進捗管理'!$V$6:$V$115&lt;=$D29)*'案件進捗管理'!$Q$6:$Q$115)</f>
         <v/>
       </c>
       <c r="O29" s="45" t="n"/>
-      <c r="P29" s="185">
-        <f>IF('キャパシティ・必要人数'!$D$21=0,"",H29/'キャパシティ・必要人数'!$D$21)</f>
+      <c r="P29" s="196">
+        <f>IF('キャパシティ・必要人数'!$D$24=0,"",H29/'キャパシティ・必要人数'!$D$24)</f>
         <v/>
       </c>
       <c r="Q29" s="45" t="n"/>
-      <c r="R29" s="186">
-        <f>IF('キャパシティ・必要人数'!$D$22=0,"",N29/'キャパシティ・必要人数'!$D$22)</f>
+      <c r="R29" s="197">
+        <f>IF('キャパシティ・必要人数'!$D$25=0,"",N29/'キャパシティ・必要人数'!$D$25)</f>
         <v/>
       </c>
       <c r="S29" s="45" t="n"/>
       <c r="T29" s="45" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="176" t="inlineStr">
+      <c r="B30" s="187" t="inlineStr">
         <is>
           <t>第5週</t>
         </is>
       </c>
-      <c r="C30" s="177" t="n"/>
-      <c r="D30" s="178" t="n">
+      <c r="C30" s="188" t="n"/>
+      <c r="D30" s="189" t="n">
         <v>46306</v>
       </c>
-      <c r="E30" s="177" t="n"/>
-      <c r="F30" s="179" t="n">
+      <c r="E30" s="188" t="n"/>
+      <c r="F30" s="190" t="n">
         <v>12</v>
       </c>
-      <c r="G30" s="177" t="n"/>
-      <c r="H30" s="180">
+      <c r="G30" s="188" t="n"/>
+      <c r="H30" s="191">
         <f>'週間スケジュール'!$F$11</f>
         <v/>
       </c>
       <c r="I30" s="45" t="n"/>
-      <c r="J30" s="181">
+      <c r="J30" s="192">
         <f>'週間スケジュール'!$G$11</f>
         <v/>
       </c>
-      <c r="K30" s="177" t="n"/>
-      <c r="L30" s="182">
+      <c r="K30" s="188" t="n"/>
+      <c r="L30" s="193">
         <f>IF('週間スケジュール'!$H$11="","",'週間スケジュール'!$H$11)</f>
         <v/>
       </c>
-      <c r="M30" s="183" t="n"/>
-      <c r="N30" s="184">
+      <c r="M30" s="194" t="n"/>
+      <c r="N30" s="195">
         <f>SUMPRODUCT(('案件進捗管理'!$V$6:$V$115&lt;&gt;"")*('案件進捗管理'!$V$6:$V$115&lt;=$D30)*'案件進捗管理'!$Q$6:$Q$115)</f>
         <v/>
       </c>
       <c r="O30" s="45" t="n"/>
-      <c r="P30" s="185">
-        <f>IF('キャパシティ・必要人数'!$D$21=0,"",H30/'キャパシティ・必要人数'!$D$21)</f>
+      <c r="P30" s="196">
+        <f>IF('キャパシティ・必要人数'!$D$24=0,"",H30/'キャパシティ・必要人数'!$D$24)</f>
         <v/>
       </c>
       <c r="Q30" s="45" t="n"/>
-      <c r="R30" s="186">
-        <f>IF('キャパシティ・必要人数'!$D$22=0,"",N30/'キャパシティ・必要人数'!$D$22)</f>
+      <c r="R30" s="197">
+        <f>IF('キャパシティ・必要人数'!$D$25=0,"",N30/'キャパシティ・必要人数'!$D$25)</f>
         <v/>
       </c>
       <c r="S30" s="45" t="n"/>
       <c r="T30" s="45" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="B31" s="176" t="inlineStr">
+      <c r="B31" s="187" t="inlineStr">
         <is>
           <t>第6週</t>
         </is>
       </c>
-      <c r="C31" s="177" t="n"/>
-      <c r="D31" s="178" t="n">
+      <c r="C31" s="188" t="n"/>
+      <c r="D31" s="189" t="n">
         <v>46313</v>
       </c>
-      <c r="E31" s="177" t="n"/>
-      <c r="F31" s="179" t="n">
+      <c r="E31" s="188" t="n"/>
+      <c r="F31" s="190" t="n">
         <v>17</v>
       </c>
-      <c r="G31" s="177" t="n"/>
-      <c r="H31" s="180">
+      <c r="G31" s="188" t="n"/>
+      <c r="H31" s="191">
         <f>'週間スケジュール'!$F$12</f>
         <v/>
       </c>
       <c r="I31" s="45" t="n"/>
-      <c r="J31" s="181">
+      <c r="J31" s="192">
         <f>'週間スケジュール'!$G$12</f>
         <v/>
       </c>
-      <c r="K31" s="177" t="n"/>
-      <c r="L31" s="182">
+      <c r="K31" s="188" t="n"/>
+      <c r="L31" s="193">
         <f>IF('週間スケジュール'!$H$12="","",'週間スケジュール'!$H$12)</f>
         <v/>
       </c>
-      <c r="M31" s="183" t="n"/>
-      <c r="N31" s="184">
+      <c r="M31" s="194" t="n"/>
+      <c r="N31" s="195">
         <f>SUMPRODUCT(('案件進捗管理'!$V$6:$V$115&lt;&gt;"")*('案件進捗管理'!$V$6:$V$115&lt;=$D31)*'案件進捗管理'!$Q$6:$Q$115)</f>
         <v/>
       </c>
       <c r="O31" s="45" t="n"/>
-      <c r="P31" s="185">
-        <f>IF('キャパシティ・必要人数'!$D$21=0,"",H31/'キャパシティ・必要人数'!$D$21)</f>
+      <c r="P31" s="196">
+        <f>IF('キャパシティ・必要人数'!$D$24=0,"",H31/'キャパシティ・必要人数'!$D$24)</f>
         <v/>
       </c>
       <c r="Q31" s="45" t="n"/>
-      <c r="R31" s="186">
-        <f>IF('キャパシティ・必要人数'!$D$22=0,"",N31/'キャパシティ・必要人数'!$D$22)</f>
+      <c r="R31" s="197">
+        <f>IF('キャパシティ・必要人数'!$D$25=0,"",N31/'キャパシティ・必要人数'!$D$25)</f>
         <v/>
       </c>
       <c r="S31" s="45" t="n"/>
       <c r="T31" s="45" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="176" t="inlineStr">
+      <c r="B32" s="187" t="inlineStr">
         <is>
           <t>第7週</t>
         </is>
       </c>
-      <c r="C32" s="177" t="n"/>
-      <c r="D32" s="178" t="n">
+      <c r="C32" s="188" t="n"/>
+      <c r="D32" s="189" t="n">
         <v>46320</v>
       </c>
-      <c r="E32" s="177" t="n"/>
-      <c r="F32" s="179" t="n">
+      <c r="E32" s="188" t="n"/>
+      <c r="F32" s="190" t="n">
         <v>25</v>
       </c>
-      <c r="G32" s="177" t="n"/>
-      <c r="H32" s="180">
+      <c r="G32" s="188" t="n"/>
+      <c r="H32" s="191">
         <f>'週間スケジュール'!$F$13</f>
         <v/>
       </c>
       <c r="I32" s="45" t="n"/>
-      <c r="J32" s="181">
+      <c r="J32" s="192">
         <f>'週間スケジュール'!$G$13</f>
         <v/>
       </c>
-      <c r="K32" s="177" t="n"/>
-      <c r="L32" s="182">
+      <c r="K32" s="188" t="n"/>
+      <c r="L32" s="193">
         <f>IF('週間スケジュール'!$H$13="","",'週間スケジュール'!$H$13)</f>
         <v/>
       </c>
-      <c r="M32" s="183" t="n"/>
-      <c r="N32" s="184">
+      <c r="M32" s="194" t="n"/>
+      <c r="N32" s="195">
         <f>SUMPRODUCT(('案件進捗管理'!$V$6:$V$115&lt;&gt;"")*('案件進捗管理'!$V$6:$V$115&lt;=$D32)*'案件進捗管理'!$Q$6:$Q$115)</f>
         <v/>
       </c>
       <c r="O32" s="45" t="n"/>
-      <c r="P32" s="185">
-        <f>IF('キャパシティ・必要人数'!$D$21=0,"",H32/'キャパシティ・必要人数'!$D$21)</f>
+      <c r="P32" s="196">
+        <f>IF('キャパシティ・必要人数'!$D$24=0,"",H32/'キャパシティ・必要人数'!$D$24)</f>
         <v/>
       </c>
       <c r="Q32" s="45" t="n"/>
-      <c r="R32" s="186">
-        <f>IF('キャパシティ・必要人数'!$D$22=0,"",N32/'キャパシティ・必要人数'!$D$22)</f>
+      <c r="R32" s="197">
+        <f>IF('キャパシティ・必要人数'!$D$25=0,"",N32/'キャパシティ・必要人数'!$D$25)</f>
         <v/>
       </c>
       <c r="S32" s="45" t="n"/>
       <c r="T32" s="45" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="B33" s="176" t="inlineStr">
+      <c r="B33" s="187" t="inlineStr">
         <is>
           <t>第8週</t>
         </is>
       </c>
-      <c r="C33" s="177" t="n"/>
-      <c r="D33" s="178" t="n">
+      <c r="C33" s="188" t="n"/>
+      <c r="D33" s="189" t="n">
         <v>46326</v>
       </c>
-      <c r="E33" s="177" t="n"/>
-      <c r="F33" s="179" t="n">
+      <c r="E33" s="188" t="n"/>
+      <c r="F33" s="190" t="n">
         <v>30</v>
       </c>
-      <c r="G33" s="177" t="n"/>
-      <c r="H33" s="180">
+      <c r="G33" s="188" t="n"/>
+      <c r="H33" s="191">
         <f>'週間スケジュール'!$F$14</f>
         <v/>
       </c>
       <c r="I33" s="45" t="n"/>
-      <c r="J33" s="181">
+      <c r="J33" s="192">
         <f>'週間スケジュール'!$G$14</f>
         <v/>
       </c>
-      <c r="K33" s="177" t="n"/>
-      <c r="L33" s="182">
+      <c r="K33" s="188" t="n"/>
+      <c r="L33" s="193">
         <f>IF('週間スケジュール'!$H$14="","",'週間スケジュール'!$H$14)</f>
         <v/>
       </c>
-      <c r="M33" s="183" t="n"/>
-      <c r="N33" s="184">
+      <c r="M33" s="194" t="n"/>
+      <c r="N33" s="195">
         <f>SUMPRODUCT(('案件進捗管理'!$V$6:$V$115&lt;&gt;"")*('案件進捗管理'!$V$6:$V$115&lt;=$D33)*'案件進捗管理'!$Q$6:$Q$115)</f>
         <v/>
       </c>
       <c r="O33" s="45" t="n"/>
-      <c r="P33" s="185">
-        <f>IF('キャパシティ・必要人数'!$D$21=0,"",H33/'キャパシティ・必要人数'!$D$21)</f>
+      <c r="P33" s="196">
+        <f>IF('キャパシティ・必要人数'!$D$24=0,"",H33/'キャパシティ・必要人数'!$D$24)</f>
         <v/>
       </c>
       <c r="Q33" s="45" t="n"/>
-      <c r="R33" s="186">
-        <f>IF('キャパシティ・必要人数'!$D$22=0,"",N33/'キャパシティ・必要人数'!$D$22)</f>
+      <c r="R33" s="197">
+        <f>IF('キャパシティ・必要人数'!$D$25=0,"",N33/'キャパシティ・必要人数'!$D$25)</f>
         <v/>
       </c>
       <c r="S33" s="45" t="n"/>
       <c r="T33" s="45" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="B34" s="187" t="inlineStr">
+      <c r="B34" s="198" t="inlineStr">
         <is>
           <t>合計 / 最終</t>
         </is>
@@ -14691,37 +14992,37 @@
       <c r="C34" s="56" t="n"/>
       <c r="D34" s="56" t="n"/>
       <c r="E34" s="56" t="n"/>
-      <c r="F34" s="188">
+      <c r="F34" s="199">
         <f>MAX(F26:F33)</f>
         <v/>
       </c>
       <c r="G34" s="56" t="n"/>
-      <c r="H34" s="188">
+      <c r="H34" s="199">
         <f>MAX(H26:H33)</f>
         <v/>
       </c>
       <c r="I34" s="56" t="n"/>
-      <c r="J34" s="189">
+      <c r="J34" s="200">
         <f>SUM(J26:J33)</f>
         <v/>
       </c>
       <c r="K34" s="56" t="n"/>
-      <c r="L34" s="190">
+      <c r="L34" s="201">
         <f>IF(COUNT(L26:L33)=0,"",SUM(L26:L33))</f>
         <v/>
       </c>
       <c r="M34" s="56" t="n"/>
-      <c r="N34" s="190">
+      <c r="N34" s="201">
         <f>MAX(N26:N33)</f>
         <v/>
       </c>
       <c r="O34" s="56" t="n"/>
-      <c r="P34" s="191">
+      <c r="P34" s="202">
         <f>MAX(P26:P33)</f>
         <v/>
       </c>
       <c r="Q34" s="56" t="n"/>
-      <c r="R34" s="191">
+      <c r="R34" s="202">
         <f>MAX(R26:R33)</f>
         <v/>
       </c>
@@ -14755,7 +15056,7 @@
       <c r="T36" s="122" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="B38" s="192" t="inlineStr">
+      <c r="B38" s="203" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
@@ -14797,27 +15098,27 @@
           <t>全社</t>
         </is>
       </c>
-      <c r="C39" s="193">
+      <c r="C39" s="204">
         <f>COUNTIF('案件進捗管理'!$E$6:$E$115,"1. 未着手")</f>
         <v/>
       </c>
-      <c r="D39" s="194">
+      <c r="D39" s="205">
         <f>COUNTIF('案件進捗管理'!$E$6:$E$115,"2. 引継ぎ中")</f>
         <v/>
       </c>
-      <c r="E39" s="195">
+      <c r="E39" s="206">
         <f>COUNTIF('案件進捗管理'!$E$6:$E$115,"3. 初回計算")</f>
         <v/>
       </c>
-      <c r="F39" s="196">
+      <c r="F39" s="207">
         <f>COUNTIF('案件進捗管理'!$E$6:$E$115,"4. 検証中")</f>
         <v/>
       </c>
-      <c r="G39" s="197">
+      <c r="G39" s="208">
         <f>COUNTIF('案件進捗管理'!$E$6:$E$115,"5. 自走可能")</f>
         <v/>
       </c>
-      <c r="H39" s="198">
+      <c r="H39" s="209">
         <f>COUNTIF('案件進捗管理'!$E$6:$E$115,"6. 完全移管")</f>
         <v/>
       </c>
@@ -14828,28 +15129,28 @@
           <t>構成比</t>
         </is>
       </c>
-      <c r="C40" s="199">
-        <f>IF('キャパシティ・必要人数'!$D$21=0,"",C39/'キャパシティ・必要人数'!$D$21)</f>
-        <v/>
-      </c>
-      <c r="D40" s="199">
-        <f>IF('キャパシティ・必要人数'!$D$21=0,"",D39/'キャパシティ・必要人数'!$D$21)</f>
-        <v/>
-      </c>
-      <c r="E40" s="199">
-        <f>IF('キャパシティ・必要人数'!$D$21=0,"",E39/'キャパシティ・必要人数'!$D$21)</f>
-        <v/>
-      </c>
-      <c r="F40" s="199">
-        <f>IF('キャパシティ・必要人数'!$D$21=0,"",F39/'キャパシティ・必要人数'!$D$21)</f>
-        <v/>
-      </c>
-      <c r="G40" s="199">
-        <f>IF('キャパシティ・必要人数'!$D$21=0,"",G39/'キャパシティ・必要人数'!$D$21)</f>
-        <v/>
-      </c>
-      <c r="H40" s="199">
-        <f>IF('キャパシティ・必要人数'!$D$21=0,"",H39/'キャパシティ・必要人数'!$D$21)</f>
+      <c r="C40" s="210">
+        <f>IF('キャパシティ・必要人数'!$D$24=0,"",C39/'キャパシティ・必要人数'!$D$24)</f>
+        <v/>
+      </c>
+      <c r="D40" s="210">
+        <f>IF('キャパシティ・必要人数'!$D$24=0,"",D39/'キャパシティ・必要人数'!$D$24)</f>
+        <v/>
+      </c>
+      <c r="E40" s="210">
+        <f>IF('キャパシティ・必要人数'!$D$24=0,"",E39/'キャパシティ・必要人数'!$D$24)</f>
+        <v/>
+      </c>
+      <c r="F40" s="210">
+        <f>IF('キャパシティ・必要人数'!$D$24=0,"",F39/'キャパシティ・必要人数'!$D$24)</f>
+        <v/>
+      </c>
+      <c r="G40" s="210">
+        <f>IF('キャパシティ・必要人数'!$D$24=0,"",G39/'キャパシティ・必要人数'!$D$24)</f>
+        <v/>
+      </c>
+      <c r="H40" s="210">
+        <f>IF('キャパシティ・必要人数'!$D$24=0,"",H39/'キャパシティ・必要人数'!$D$24)</f>
         <v/>
       </c>
     </row>
@@ -14880,12 +15181,12 @@
       <c r="T42" s="122" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="192" t="inlineStr">
+      <c r="B43" s="203" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C43" s="192" t="inlineStr">
+      <c r="C43" s="203" t="inlineStr">
         <is>
           <t>月あたり工数（h）</t>
         </is>
@@ -14897,11 +15198,11 @@
           <t>現在処理能力（月）</t>
         </is>
       </c>
-      <c r="C44" s="200">
-        <f>'キャパシティ・必要人数'!$D$29</f>
-        <v/>
-      </c>
-      <c r="D44" s="201" t="inlineStr">
+      <c r="C44" s="211">
+        <f>'キャパシティ・必要人数'!$D$32</f>
+        <v/>
+      </c>
+      <c r="D44" s="212" t="inlineStr">
         <is>
           <t>必要処理能力が現在処理能力を上回る場合は増員が必要です。不足分 ÷ 1人あたり月間有効稼働時間 ＝ 追加必要人数（キャパシティシートで自動算出）。</t>
         </is>
@@ -14913,8 +15214,8 @@
           <t>必要処理能力（月）</t>
         </is>
       </c>
-      <c r="C45" s="202">
-        <f>'キャパシティ・必要人数'!$D$23</f>
+      <c r="C45" s="213">
+        <f>'キャパシティ・必要人数'!$D$26</f>
         <v/>
       </c>
     </row>
@@ -15007,7 +15308,7 @@
     <row r="108" ht="32" customHeight="1">
       <c r="A108" s="40" t="inlineStr">
         <is>
-          <t>【進捗管理ルール】このプロジェクトは「何社移管したか」だけでは判断しません。①件数進捗（何社が各ステータスまで進んだか）②工数進捗（全体工数のうち何時間分を移管できたか）③自走進捗（何社がAn-field様の日常的な確認なしで運用できるか）の3軸で評価します。</t>
+          <t>【10月末時点で確認すべき判断材料】　① 実運用済み企業数　② 自走可能企業数　③ 完全移管企業数　④ 残企業数　⑤ 残工数　⑥ 必要追加人数　⑦ 1人あたり処理可能工数・1人あたり処理可能社数　⑧ 月あたり移管可能件数・今後の移管ペース（社/週）　→ ⑦⑧の詳細は「キャパシティ・必要人数」シートで自動算出されます。</t>
         </is>
       </c>
       <c r="B108" s="41" t="n"/>
@@ -15030,10 +15331,10 @@
       <c r="S108" s="41" t="n"/>
       <c r="T108" s="41" t="n"/>
     </row>
-    <row r="109" ht="28" customHeight="1">
+    <row r="109" ht="32" customHeight="1">
       <c r="A109" s="39" t="inlineStr">
         <is>
-          <t>【完全移管の定義】資料回収・給与計算・不明点対応・顧問先とのやり取り・納品・担当者管理まで、An-field様の日常的な管理なしで完結する状態。「給与計算ができる状態」は完全移管ではありません。</t>
+          <t>【企業数だけで見ないための重点KPI（10/12週〜）】① 処理できた総工数 ＝ KPIカード「移管済み工数」　② An-field様の確認が不要だった企業数 ＝ KPIカード「完全移管企業数」　③ 担当者単独で処理できた企業数 ＝ KPIカード「自走可能企業数」</t>
         </is>
       </c>
       <c r="B109" s="14" t="n"/>
@@ -15056,87 +15357,138 @@
       <c r="S109" s="14" t="n"/>
       <c r="T109" s="14" t="n"/>
     </row>
-    <row r="110" ht="42" customHeight="1">
-      <c r="A110" s="105" t="inlineStr">
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="40" t="inlineStr">
+        <is>
+          <t>【進捗管理ルール】このプロジェクトは「何社移管したか」だけでは判断しません。①件数進捗（何社が各ステータスまで進んだか）②工数進捗（全体工数のうち何時間分を移管できたか）③自走進捗（何社がAn-field様の日常的な確認なしで運用できるか）の3軸で評価します。</t>
+        </is>
+      </c>
+      <c r="B110" s="41" t="n"/>
+      <c r="C110" s="41" t="n"/>
+      <c r="D110" s="41" t="n"/>
+      <c r="E110" s="41" t="n"/>
+      <c r="F110" s="41" t="n"/>
+      <c r="G110" s="41" t="n"/>
+      <c r="H110" s="41" t="n"/>
+      <c r="I110" s="41" t="n"/>
+      <c r="J110" s="41" t="n"/>
+      <c r="K110" s="41" t="n"/>
+      <c r="L110" s="41" t="n"/>
+      <c r="M110" s="41" t="n"/>
+      <c r="N110" s="41" t="n"/>
+      <c r="O110" s="41" t="n"/>
+      <c r="P110" s="41" t="n"/>
+      <c r="Q110" s="41" t="n"/>
+      <c r="R110" s="41" t="n"/>
+      <c r="S110" s="41" t="n"/>
+      <c r="T110" s="41" t="n"/>
+    </row>
+    <row r="111" ht="28" customHeight="1">
+      <c r="A111" s="39" t="inlineStr">
+        <is>
+          <t>【完全移管の定義】資料回収・給与計算・不明点対応・顧問先とのやり取り・納品・担当者管理まで、An-field様の日常的な管理なしで完結する状態。「給与計算ができる状態」は完全移管ではありません。</t>
+        </is>
+      </c>
+      <c r="B111" s="14" t="n"/>
+      <c r="C111" s="14" t="n"/>
+      <c r="D111" s="14" t="n"/>
+      <c r="E111" s="14" t="n"/>
+      <c r="F111" s="14" t="n"/>
+      <c r="G111" s="14" t="n"/>
+      <c r="H111" s="14" t="n"/>
+      <c r="I111" s="14" t="n"/>
+      <c r="J111" s="14" t="n"/>
+      <c r="K111" s="14" t="n"/>
+      <c r="L111" s="14" t="n"/>
+      <c r="M111" s="14" t="n"/>
+      <c r="N111" s="14" t="n"/>
+      <c r="O111" s="14" t="n"/>
+      <c r="P111" s="14" t="n"/>
+      <c r="Q111" s="14" t="n"/>
+      <c r="R111" s="14" t="n"/>
+      <c r="S111" s="14" t="n"/>
+      <c r="T111" s="14" t="n"/>
+    </row>
+    <row r="112" ht="42" customHeight="1">
+      <c r="A112" s="105" t="inlineStr">
         <is>
           <t>【10月末のゴール】100〜110社の完全移管ではありません。①先行企業で実運用が成立　②企業別工数の把握　③企業別難易度の整理　④秘書／ワーカーの役割分担成立　⑤1人あたり処理能力の把握　⑥現在人員で何社まで運用可能かが判明　⑦完全移管までの残工数が判明　⑧追加必要人員数が判明　⑨今後の移管ペースを数値で設計できる　この状態がゴールです。</t>
         </is>
       </c>
-      <c r="B110" s="43" t="n"/>
-      <c r="C110" s="43" t="n"/>
-      <c r="D110" s="43" t="n"/>
-      <c r="E110" s="43" t="n"/>
-      <c r="F110" s="43" t="n"/>
-      <c r="G110" s="43" t="n"/>
-      <c r="H110" s="43" t="n"/>
-      <c r="I110" s="43" t="n"/>
-      <c r="J110" s="43" t="n"/>
-      <c r="K110" s="43" t="n"/>
-      <c r="L110" s="43" t="n"/>
-      <c r="M110" s="43" t="n"/>
-      <c r="N110" s="43" t="n"/>
-      <c r="O110" s="43" t="n"/>
-      <c r="P110" s="43" t="n"/>
-      <c r="Q110" s="43" t="n"/>
-      <c r="R110" s="43" t="n"/>
-      <c r="S110" s="43" t="n"/>
-      <c r="T110" s="43" t="n"/>
-    </row>
-    <row r="111" ht="32" customHeight="1">
-      <c r="A111" s="139" t="inlineStr">
+      <c r="B112" s="43" t="n"/>
+      <c r="C112" s="43" t="n"/>
+      <c r="D112" s="43" t="n"/>
+      <c r="E112" s="43" t="n"/>
+      <c r="F112" s="43" t="n"/>
+      <c r="G112" s="43" t="n"/>
+      <c r="H112" s="43" t="n"/>
+      <c r="I112" s="43" t="n"/>
+      <c r="J112" s="43" t="n"/>
+      <c r="K112" s="43" t="n"/>
+      <c r="L112" s="43" t="n"/>
+      <c r="M112" s="43" t="n"/>
+      <c r="N112" s="43" t="n"/>
+      <c r="O112" s="43" t="n"/>
+      <c r="P112" s="43" t="n"/>
+      <c r="Q112" s="43" t="n"/>
+      <c r="R112" s="43" t="n"/>
+      <c r="S112" s="43" t="n"/>
+      <c r="T112" s="43" t="n"/>
+    </row>
+    <row r="113" ht="32" customHeight="1">
+      <c r="A113" s="141" t="inlineStr">
         <is>
           <t>【暫定計画値】9月：先行引継ぎ10〜15社程度／10月前半：実運用累計10〜20社程度／10月末：実運用累計25〜35社程度。いずれも確定値ではなく暫定計画値です。会社別工数・実績確認後に更新してください。件数目標を達成するために無理に企業を移管せず、実工数と品質をもとに件数を調整してください。</t>
         </is>
       </c>
-      <c r="B111" s="140" t="n"/>
-      <c r="C111" s="140" t="n"/>
-      <c r="D111" s="140" t="n"/>
-      <c r="E111" s="140" t="n"/>
-      <c r="F111" s="140" t="n"/>
-      <c r="G111" s="140" t="n"/>
-      <c r="H111" s="140" t="n"/>
-      <c r="I111" s="140" t="n"/>
-      <c r="J111" s="140" t="n"/>
-      <c r="K111" s="140" t="n"/>
-      <c r="L111" s="140" t="n"/>
-      <c r="M111" s="140" t="n"/>
-      <c r="N111" s="140" t="n"/>
-      <c r="O111" s="140" t="n"/>
-      <c r="P111" s="140" t="n"/>
-      <c r="Q111" s="140" t="n"/>
-      <c r="R111" s="140" t="n"/>
-      <c r="S111" s="140" t="n"/>
-      <c r="T111" s="140" t="n"/>
-    </row>
-    <row r="112" ht="22" customHeight="1">
-      <c r="A112" s="44" t="inlineStr">
+      <c r="B113" s="142" t="n"/>
+      <c r="C113" s="142" t="n"/>
+      <c r="D113" s="142" t="n"/>
+      <c r="E113" s="142" t="n"/>
+      <c r="F113" s="142" t="n"/>
+      <c r="G113" s="142" t="n"/>
+      <c r="H113" s="142" t="n"/>
+      <c r="I113" s="142" t="n"/>
+      <c r="J113" s="142" t="n"/>
+      <c r="K113" s="142" t="n"/>
+      <c r="L113" s="142" t="n"/>
+      <c r="M113" s="142" t="n"/>
+      <c r="N113" s="142" t="n"/>
+      <c r="O113" s="142" t="n"/>
+      <c r="P113" s="142" t="n"/>
+      <c r="Q113" s="142" t="n"/>
+      <c r="R113" s="142" t="n"/>
+      <c r="S113" s="142" t="n"/>
+      <c r="T113" s="142" t="n"/>
+    </row>
+    <row r="114" ht="22" customHeight="1">
+      <c r="A114" s="44" t="inlineStr">
         <is>
           <t>【凡例】薄い黄色＝手入力　／　薄いグレー＝自動計算　／　白＝暫定計画値（固定）　／　赤＝警告・不足のみ</t>
         </is>
       </c>
-      <c r="B112" s="45" t="n"/>
-      <c r="C112" s="45" t="n"/>
-      <c r="D112" s="45" t="n"/>
-      <c r="E112" s="45" t="n"/>
-      <c r="F112" s="45" t="n"/>
-      <c r="G112" s="45" t="n"/>
-      <c r="H112" s="45" t="n"/>
-      <c r="I112" s="45" t="n"/>
-      <c r="J112" s="45" t="n"/>
-      <c r="K112" s="45" t="n"/>
-      <c r="L112" s="45" t="n"/>
-      <c r="M112" s="45" t="n"/>
-      <c r="N112" s="45" t="n"/>
-      <c r="O112" s="45" t="n"/>
-      <c r="P112" s="45" t="n"/>
-      <c r="Q112" s="45" t="n"/>
-      <c r="R112" s="45" t="n"/>
-      <c r="S112" s="45" t="n"/>
-      <c r="T112" s="45" t="n"/>
+      <c r="B114" s="45" t="n"/>
+      <c r="C114" s="45" t="n"/>
+      <c r="D114" s="45" t="n"/>
+      <c r="E114" s="45" t="n"/>
+      <c r="F114" s="45" t="n"/>
+      <c r="G114" s="45" t="n"/>
+      <c r="H114" s="45" t="n"/>
+      <c r="I114" s="45" t="n"/>
+      <c r="J114" s="45" t="n"/>
+      <c r="K114" s="45" t="n"/>
+      <c r="L114" s="45" t="n"/>
+      <c r="M114" s="45" t="n"/>
+      <c r="N114" s="45" t="n"/>
+      <c r="O114" s="45" t="n"/>
+      <c r="P114" s="45" t="n"/>
+      <c r="Q114" s="45" t="n"/>
+      <c r="R114" s="45" t="n"/>
+      <c r="S114" s="45" t="n"/>
+      <c r="T114" s="45" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="148">
-    <mergeCell ref="L19:T21"/>
+  <mergeCells count="155">
     <mergeCell ref="F29:G29"/>
     <mergeCell ref="R27:T27"/>
     <mergeCell ref="F25:G25"/>
@@ -15148,7 +15500,9 @@
     <mergeCell ref="Q13:T13"/>
     <mergeCell ref="L17:O17"/>
     <mergeCell ref="Q7:T7"/>
+    <mergeCell ref="Q21:T21"/>
     <mergeCell ref="A108:T108"/>
+    <mergeCell ref="L19:O19"/>
     <mergeCell ref="L29:M29"/>
     <mergeCell ref="N29:O29"/>
     <mergeCell ref="G8:J8"/>
@@ -15176,7 +15530,9 @@
     <mergeCell ref="D34:E34"/>
     <mergeCell ref="G20:J20"/>
     <mergeCell ref="F34:G34"/>
+    <mergeCell ref="A114:T114"/>
     <mergeCell ref="Q17:T17"/>
+    <mergeCell ref="L21:O21"/>
     <mergeCell ref="N25:O25"/>
     <mergeCell ref="Q11:T11"/>
     <mergeCell ref="P25:Q25"/>
@@ -15208,6 +15564,7 @@
     <mergeCell ref="P30:Q30"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="A109:T109"/>
+    <mergeCell ref="L20:O20"/>
     <mergeCell ref="R31:T31"/>
     <mergeCell ref="A111:T111"/>
     <mergeCell ref="J29:K29"/>
@@ -15234,6 +15591,8 @@
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="L25:M25"/>
     <mergeCell ref="D28:E28"/>
+    <mergeCell ref="A113:T113"/>
+    <mergeCell ref="Q20:T20"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="G13:J13"/>
     <mergeCell ref="B17:E17"/>
@@ -15275,6 +15634,7 @@
     <mergeCell ref="G19:J19"/>
     <mergeCell ref="H27:I27"/>
     <mergeCell ref="D44:T45"/>
+    <mergeCell ref="Q19:T19"/>
     <mergeCell ref="L34:M34"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="N34:O34"/>
